--- a/26spring list and group 260515.xlsx
+++ b/26spring list and group 260515.xlsx
@@ -1,36 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\26spring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lzz/github_teaching/emetrics26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C18E7E0-77FC-4F59-B378-628F504829A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7064E4F-C834-8F4A-9FA8-772B7930AB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="计量进度" sheetId="5" r:id="rId1"/>
     <sheet name="publish" sheetId="12" r:id="rId2"/>
-    <sheet name="W3选题" sheetId="10" r:id="rId3"/>
-    <sheet name="W7回归人资" sheetId="13" r:id="rId4"/>
-    <sheet name="W10人资" sheetId="15" r:id="rId5"/>
-    <sheet name="W10工管" sheetId="16" r:id="rId6"/>
-    <sheet name="Sheet4" sheetId="18" r:id="rId7"/>
-    <sheet name="Sheet2" sheetId="17" r:id="rId8"/>
-    <sheet name="W7回归工管" sheetId="14" r:id="rId9"/>
-    <sheet name="分组定稿" sheetId="11" r:id="rId10"/>
-    <sheet name="24人力" sheetId="2" r:id="rId11"/>
-    <sheet name="24工管" sheetId="1" r:id="rId12"/>
-    <sheet name="25会计2" sheetId="4" r:id="rId13"/>
-    <sheet name="25金融2" sheetId="3" r:id="rId14"/>
-    <sheet name="统计分组" sheetId="9" r:id="rId15"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId16"/>
-    <sheet name="第1周人力" sheetId="6" r:id="rId17"/>
-    <sheet name="Sheet3" sheetId="7" r:id="rId18"/>
+    <sheet name="Sheet5" sheetId="19" r:id="rId3"/>
+    <sheet name="W3选题" sheetId="10" r:id="rId4"/>
+    <sheet name="W7回归人资" sheetId="13" r:id="rId5"/>
+    <sheet name="W10人资" sheetId="15" r:id="rId6"/>
+    <sheet name="W10工管" sheetId="16" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="18" r:id="rId8"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId9"/>
+    <sheet name="W7回归工管" sheetId="14" r:id="rId10"/>
+    <sheet name="分组定稿" sheetId="11" r:id="rId11"/>
+    <sheet name="24人力" sheetId="2" r:id="rId12"/>
+    <sheet name="24工管" sheetId="1" r:id="rId13"/>
+    <sheet name="25会计2" sheetId="4" r:id="rId14"/>
+    <sheet name="25金融2" sheetId="3" r:id="rId15"/>
+    <sheet name="统计分组" sheetId="9" r:id="rId16"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId17"/>
+    <sheet name="第1周人力" sheetId="6" r:id="rId18"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2954" uniqueCount="1308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="1309">
   <si>
     <t>华南农业大学学生课堂考勤表</t>
   </si>
@@ -4556,6 +4557,10 @@
   </si>
   <si>
     <t>缺定性变量，没有EVIEWS，整理数据，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>26春 经济计量学分组名单</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4868,7 +4873,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5008,9 +5013,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5038,13 +5040,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
@@ -5052,9 +5051,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -5064,6 +5060,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5086,11 +5085,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5427,24 +5423,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E28D1B2D-9959-5042-B92E-447F06702482}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" style="26" customWidth="1"/>
-    <col min="4" max="6" width="10.77734375" style="26"/>
-    <col min="7" max="7" width="13.77734375" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" style="25" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="26" customWidth="1"/>
+    <col min="3" max="3" width="6.5" style="26" customWidth="1"/>
+    <col min="4" max="6" width="10.83203125" style="26"/>
+    <col min="7" max="7" width="13.83203125" style="26" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" style="26" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="54.33203125" style="23" customWidth="1"/>
-    <col min="10" max="11" width="10.77734375" style="23"/>
+    <col min="10" max="11" width="10.83203125" style="23"/>
     <col min="12" max="12" width="6.33203125" style="23" customWidth="1"/>
-    <col min="13" max="15" width="20.77734375" style="23" customWidth="1"/>
-    <col min="16" max="17" width="21.109375" style="23" customWidth="1"/>
-    <col min="18" max="18" width="14.109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="10.77734375" style="26"/>
+    <col min="13" max="15" width="20.83203125" style="23" customWidth="1"/>
+    <col min="16" max="17" width="21.1640625" style="23" customWidth="1"/>
+    <col min="18" max="18" width="14.1640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="10.83203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="69">
+    <row r="1" spans="1:18" ht="80">
       <c r="A1" s="25" t="s">
         <v>783</v>
       </c>
@@ -5500,7 +5496,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="69">
+    <row r="2" spans="1:18" ht="80">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -5551,7 +5547,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="96.6">
+    <row r="3" spans="1:18" ht="96">
       <c r="A3" s="25">
         <v>2</v>
       </c>
@@ -5598,7 +5594,7 @@
       <c r="H4" s="25"/>
       <c r="I4" s="24"/>
     </row>
-    <row r="5" spans="1:18" ht="124.2">
+    <row r="5" spans="1:18" ht="144">
       <c r="A5" s="25">
         <v>4</v>
       </c>
@@ -5646,7 +5642,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="179.4">
+    <row r="6" spans="1:18" ht="192">
       <c r="A6" s="25">
         <v>5</v>
       </c>
@@ -5695,7 +5691,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="19.05" customHeight="1">
+    <row r="7" spans="1:18" ht="19" customHeight="1">
       <c r="A7" s="25">
         <v>6</v>
       </c>
@@ -5746,7 +5742,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="234.6">
+    <row r="8" spans="1:18" ht="256">
       <c r="A8" s="25">
         <v>7</v>
       </c>
@@ -5792,7 +5788,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="124.2">
+    <row r="9" spans="1:18" ht="128">
       <c r="A9" s="25">
         <v>8</v>
       </c>
@@ -5841,7 +5837,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="151.80000000000001">
+    <row r="10" spans="1:18" ht="160">
       <c r="A10" s="25">
         <v>9</v>
       </c>
@@ -5890,7 +5886,7 @@
       </c>
       <c r="Q10" s="27"/>
     </row>
-    <row r="11" spans="1:18" ht="151.80000000000001">
+    <row r="11" spans="1:18" ht="176">
       <c r="A11" s="25">
         <v>10</v>
       </c>
@@ -5941,7 +5937,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="27.6">
+    <row r="12" spans="1:18" ht="32">
       <c r="A12" s="25">
         <v>11</v>
       </c>
@@ -5968,7 +5964,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="124.2">
+    <row r="13" spans="1:18" ht="144">
       <c r="A13" s="25">
         <v>12</v>
       </c>
@@ -6019,7 +6015,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="110.4">
+    <row r="14" spans="1:18" ht="112">
       <c r="A14" s="25">
         <v>13</v>
       </c>
@@ -6070,7 +6066,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="151.80000000000001">
+    <row r="15" spans="1:18" ht="176">
       <c r="A15" s="25">
         <v>14</v>
       </c>
@@ -6143,7 +6139,7 @@
       </c>
       <c r="I16" s="24"/>
     </row>
-    <row r="17" spans="1:17" ht="207">
+    <row r="17" spans="1:17" ht="224">
       <c r="A17" s="25">
         <v>16</v>
       </c>
@@ -6194,7 +6190,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="138">
+    <row r="18" spans="1:17" ht="144">
       <c r="A18" s="25">
         <v>17</v>
       </c>
@@ -6249,7 +6245,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="69">
+    <row r="24" spans="1:17" ht="80">
       <c r="A24" s="25" t="s">
         <v>783</v>
       </c>
@@ -6299,7 +6295,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="82.8">
+    <row r="25" spans="1:17" ht="96">
       <c r="A25" s="25">
         <v>1</v>
       </c>
@@ -6350,7 +6346,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="151.80000000000001">
+    <row r="26" spans="1:17" ht="160">
       <c r="A26" s="25">
         <v>2</v>
       </c>
@@ -6399,7 +6395,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="110.4">
+    <row r="27" spans="1:17" ht="112">
       <c r="A27" s="25">
         <v>3</v>
       </c>
@@ -6448,7 +6444,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="124.2">
+    <row r="28" spans="1:17" ht="144">
       <c r="A28" s="25">
         <v>4</v>
       </c>
@@ -6496,7 +6492,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="27.6">
+    <row r="29" spans="1:17" ht="32">
       <c r="A29" s="25">
         <v>5</v>
       </c>
@@ -6547,7 +6543,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="165.6">
+    <row r="30" spans="1:17" ht="176">
       <c r="A30" s="25">
         <v>6</v>
       </c>
@@ -6595,7 +6591,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="96.6">
+    <row r="31" spans="1:17" ht="112">
       <c r="A31" s="25">
         <v>7</v>
       </c>
@@ -6646,7 +6642,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="69">
+    <row r="32" spans="1:17" ht="80">
       <c r="A32" s="25">
         <v>8</v>
       </c>
@@ -6697,7 +6693,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="96.6">
+    <row r="33" spans="1:18" ht="96">
       <c r="A33" s="25">
         <v>9</v>
       </c>
@@ -6751,7 +6747,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="124.2">
+    <row r="34" spans="1:18" ht="144">
       <c r="A34" s="25">
         <v>10</v>
       </c>
@@ -6802,7 +6798,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="220.8">
+    <row r="35" spans="1:18" ht="224">
       <c r="A35" s="25">
         <v>11</v>
       </c>
@@ -6856,7 +6852,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="96.6">
+    <row r="36" spans="1:18" ht="112">
       <c r="A36" s="25">
         <v>12</v>
       </c>
@@ -6903,7 +6899,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="207">
+    <row r="37" spans="1:18" ht="240">
       <c r="A37" s="25">
         <v>13</v>
       </c>
@@ -6954,7 +6950,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="276">
+    <row r="38" spans="1:18" ht="304">
       <c r="A38" s="25">
         <v>14</v>
       </c>
@@ -7005,7 +7001,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="55.2">
+    <row r="39" spans="1:18" ht="64">
       <c r="A39" s="25">
         <v>15</v>
       </c>
@@ -7053,7 +7049,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="69">
+    <row r="40" spans="1:18" ht="64">
       <c r="A40" s="25">
         <v>16</v>
       </c>
@@ -7101,7 +7097,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="345">
+    <row r="41" spans="1:18" ht="365">
       <c r="A41" s="25">
         <v>17</v>
       </c>
@@ -7171,20 +7167,530 @@
   </sortState>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAD788D-949A-49FB-B3CF-88BF7FE61F68}">
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="79.5" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="16">
+      <c r="A1" s="30" t="s">
+        <v>783</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="H1" s="57" t="s">
+        <v>1197</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>496</v>
+      </c>
+      <c r="C2" s="35">
+        <v>4</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>498</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>499</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>500</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>501</v>
+      </c>
+      <c r="C3" s="35">
+        <v>4</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>502</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>503</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>504</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>505</v>
+      </c>
+      <c r="C4" s="35">
+        <v>1</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>506</v>
+      </c>
+      <c r="C5" s="35">
+        <v>5</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>507</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>508</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>509</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>510</v>
+      </c>
+      <c r="C6" s="35">
+        <v>3</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>511</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>512</v>
+      </c>
+      <c r="G6" s="35"/>
+      <c r="H6" s="56" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="16">
+      <c r="A7" s="34">
+        <v>6</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>513</v>
+      </c>
+      <c r="C7" s="35">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>514</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>515</v>
+      </c>
+      <c r="H7" s="56" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16">
+      <c r="A8" s="34">
+        <v>7</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="C8" s="35">
+        <v>3</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="G8" s="35"/>
+      <c r="H8" s="56" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="16">
+      <c r="A9" s="34">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C9" s="35">
+        <v>3</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>521</v>
+      </c>
+      <c r="G9" s="35"/>
+      <c r="H9" s="56" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16">
+      <c r="A10" s="34">
+        <v>9</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="C10" s="35">
+        <v>4</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>524</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>525</v>
+      </c>
+      <c r="H10" s="56" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="K10" s="35" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="16">
+      <c r="A11" s="34">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="C11" s="35">
+        <v>4</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>529</v>
+      </c>
+      <c r="H11" s="56" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16">
+      <c r="A12" s="34">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>530</v>
+      </c>
+      <c r="C12" s="35">
+        <v>4</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>531</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>532</v>
+      </c>
+      <c r="H12" s="56" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="16">
+      <c r="A13" s="34">
+        <v>12</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>533</v>
+      </c>
+      <c r="C13" s="35">
+        <v>4</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>534</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>535</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>536</v>
+      </c>
+      <c r="H13" s="56" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16">
+      <c r="A14" s="34">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>537</v>
+      </c>
+      <c r="C14" s="35">
+        <v>4</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>540</v>
+      </c>
+      <c r="H14" s="56" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16">
+      <c r="A15" s="34">
+        <v>14</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>541</v>
+      </c>
+      <c r="C15" s="35">
+        <v>4</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>542</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>543</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>544</v>
+      </c>
+      <c r="H15" s="56" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16">
+      <c r="A16" s="34">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>552</v>
+      </c>
+      <c r="C16" s="35">
+        <v>3</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>553</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>554</v>
+      </c>
+      <c r="G16" s="35"/>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16" s="35" t="s">
+        <v>552</v>
+      </c>
+      <c r="K16" s="35" t="s">
+        <v>553</v>
+      </c>
+      <c r="L16" s="35" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="16">
+      <c r="A17" s="34">
+        <v>16</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>545</v>
+      </c>
+      <c r="C17" s="35">
+        <v>4</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>546</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>547</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>548</v>
+      </c>
+      <c r="H17" s="56" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="16">
+      <c r="A18" s="41">
+        <v>17</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>549</v>
+      </c>
+      <c r="C18" s="42">
+        <v>3</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>550</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>551</v>
+      </c>
+      <c r="G18" s="42"/>
+      <c r="H18" s="56" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" s="42" t="s">
+        <v>549</v>
+      </c>
+      <c r="K18" s="42" t="s">
+        <v>551</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFADBF3-7ED3-4149-8A52-E80B7FE0D6FF}">
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" ht="16">
       <c r="A1" s="9" t="s">
         <v>783</v>
       </c>
@@ -7210,7 +7716,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15">
+    <row r="2" spans="1:8" ht="16">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -7234,7 +7740,7 @@
       </c>
       <c r="H2" s="9"/>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:8" ht="16">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -7258,7 +7764,7 @@
       </c>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:8" ht="15">
+    <row r="4" spans="1:8" ht="16">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -7276,7 +7782,7 @@
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
     </row>
-    <row r="5" spans="1:8" ht="15">
+    <row r="5" spans="1:8" ht="16">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -7300,7 +7806,7 @@
       </c>
       <c r="H5" s="9"/>
     </row>
-    <row r="6" spans="1:8" ht="15">
+    <row r="6" spans="1:8" ht="16">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -7322,7 +7828,7 @@
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
     </row>
-    <row r="7" spans="1:8" ht="15">
+    <row r="7" spans="1:8" ht="16">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -7346,7 +7852,7 @@
       </c>
       <c r="H7" s="9"/>
     </row>
-    <row r="8" spans="1:8" ht="15">
+    <row r="8" spans="1:8" ht="16">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -7368,7 +7874,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="1:8" ht="15">
+    <row r="9" spans="1:8" ht="16">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -7390,7 +7896,7 @@
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
     </row>
-    <row r="10" spans="1:8" ht="15">
+    <row r="10" spans="1:8" ht="16">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -7414,7 +7920,7 @@
       </c>
       <c r="H10" s="9"/>
     </row>
-    <row r="11" spans="1:8" ht="15">
+    <row r="11" spans="1:8" ht="16">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -7438,7 +7944,7 @@
       </c>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" ht="15">
+    <row r="12" spans="1:8" ht="16">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -7462,7 +7968,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" ht="15">
+    <row r="13" spans="1:8" ht="16">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -7486,7 +7992,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" ht="15">
+    <row r="14" spans="1:8" ht="16">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -7510,7 +8016,7 @@
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" ht="15">
+    <row r="15" spans="1:8" ht="16">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -7534,7 +8040,7 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" ht="15">
+    <row r="16" spans="1:8" ht="16">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -7558,7 +8064,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15">
+    <row r="17" spans="1:8" ht="16">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -7582,7 +8088,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" ht="15">
+    <row r="18" spans="1:8" ht="16">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -7604,7 +8110,7 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" ht="15">
+    <row r="19" spans="1:8" ht="16">
       <c r="A19" s="9"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -7614,7 +8120,7 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
     </row>
-    <row r="20" spans="1:8" ht="15">
+    <row r="20" spans="1:8" ht="16">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
         <v>784</v>
@@ -7629,7 +8135,7 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" ht="15">
+    <row r="21" spans="1:8" ht="16">
       <c r="A21" s="9"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -7639,7 +8145,7 @@
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8" ht="15">
+    <row r="22" spans="1:8" ht="16">
       <c r="A22" s="9"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -7649,7 +8155,7 @@
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
     </row>
-    <row r="23" spans="1:8" ht="15">
+    <row r="23" spans="1:8" ht="16">
       <c r="A23" s="9"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -7659,7 +8165,7 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8" ht="15">
+    <row r="24" spans="1:8" ht="16">
       <c r="A24" s="9" t="s">
         <v>783</v>
       </c>
@@ -7685,7 +8191,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15">
+    <row r="25" spans="1:8" ht="16">
       <c r="A25" s="9">
         <v>1</v>
       </c>
@@ -7709,7 +8215,7 @@
       </c>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" ht="15">
+    <row r="26" spans="1:8" ht="16">
       <c r="A26" s="9">
         <v>2</v>
       </c>
@@ -7731,7 +8237,7 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" ht="15">
+    <row r="27" spans="1:8" ht="16">
       <c r="A27" s="9">
         <v>3</v>
       </c>
@@ -7753,7 +8259,7 @@
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" ht="15">
+    <row r="28" spans="1:8" ht="16">
       <c r="A28" s="9">
         <v>4</v>
       </c>
@@ -7777,7 +8283,7 @@
       </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" ht="15">
+    <row r="29" spans="1:8" ht="16">
       <c r="A29" s="9">
         <v>5</v>
       </c>
@@ -7801,7 +8307,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" ht="15">
+    <row r="30" spans="1:8" ht="16">
       <c r="A30" s="9">
         <v>6</v>
       </c>
@@ -7825,7 +8331,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" ht="15">
+    <row r="31" spans="1:8" ht="16">
       <c r="A31" s="9">
         <v>7</v>
       </c>
@@ -7849,7 +8355,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" ht="15">
+    <row r="32" spans="1:8" ht="16">
       <c r="A32" s="9">
         <v>8</v>
       </c>
@@ -7873,7 +8379,7 @@
       </c>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" ht="15">
+    <row r="33" spans="1:8" ht="16">
       <c r="A33" s="9">
         <v>9</v>
       </c>
@@ -7897,7 +8403,7 @@
       </c>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" ht="15">
+    <row r="34" spans="1:8" ht="16">
       <c r="A34" s="9">
         <v>10</v>
       </c>
@@ -7921,7 +8427,7 @@
       </c>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8" ht="15">
+    <row r="35" spans="1:8" ht="16">
       <c r="A35" s="9">
         <v>11</v>
       </c>
@@ -7945,7 +8451,7 @@
       </c>
       <c r="H35" s="9"/>
     </row>
-    <row r="36" spans="1:8" ht="15">
+    <row r="36" spans="1:8" ht="16">
       <c r="A36" s="9">
         <v>12</v>
       </c>
@@ -7969,7 +8475,7 @@
       </c>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="1:8" ht="15">
+    <row r="37" spans="1:8" ht="16">
       <c r="A37" s="9">
         <v>13</v>
       </c>
@@ -7993,7 +8499,7 @@
       </c>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8" ht="15">
+    <row r="38" spans="1:8" ht="16">
       <c r="A38" s="9">
         <v>14</v>
       </c>
@@ -8017,7 +8523,7 @@
       </c>
       <c r="H38" s="9"/>
     </row>
-    <row r="39" spans="1:8" ht="15">
+    <row r="39" spans="1:8" ht="16">
       <c r="A39" s="9">
         <v>15</v>
       </c>
@@ -8041,7 +8547,7 @@
       </c>
       <c r="H39" s="9"/>
     </row>
-    <row r="40" spans="1:8" ht="15">
+    <row r="40" spans="1:8" ht="16">
       <c r="A40" s="9">
         <v>16</v>
       </c>
@@ -8065,7 +8571,7 @@
       </c>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:8" ht="15">
+    <row r="41" spans="1:8" ht="16">
       <c r="A41" s="9">
         <v>17</v>
       </c>
@@ -8092,108 +8598,109 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB053F64-76DE-4B4F-BF9D-E00DD8E03B9E}">
   <dimension ref="A1:Y74"/>
-  <sheetFormatPr defaultColWidth="9.77734375" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="4.109375" customWidth="1"/>
+    <col min="5" max="6" width="4.1640625" customWidth="1"/>
     <col min="7" max="25" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="66"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-    </row>
-    <row r="3" spans="1:25" ht="19.95" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+    </row>
+    <row r="3" spans="1:25" ht="20" customHeight="1">
+      <c r="A3" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="66"/>
+      <c r="Y3" s="66"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -10730,109 +11237,110 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y66"/>
-  <sheetFormatPr defaultColWidth="9.77734375" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="6" width="4.109375" customWidth="1"/>
+    <col min="5" max="6" width="4.1640625" customWidth="1"/>
     <col min="7" max="25" width="3" customWidth="1"/>
-    <col min="26" max="27" width="9.77734375" customWidth="1"/>
+    <col min="26" max="27" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="69"/>
-      <c r="W1" s="69"/>
-      <c r="X1" s="69"/>
-      <c r="Y1" s="69"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="70"/>
-      <c r="V2" s="70"/>
-      <c r="W2" s="70"/>
-      <c r="X2" s="70"/>
-      <c r="Y2" s="70"/>
-    </row>
-    <row r="3" spans="1:25" ht="19.95" customHeight="1">
-      <c r="A3" s="71" t="s">
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+    </row>
+    <row r="3" spans="1:25" ht="20" customHeight="1">
+      <c r="A3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="71"/>
-      <c r="Y3" s="71"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
+      <c r="W3" s="69"/>
+      <c r="X3" s="69"/>
+      <c r="Y3" s="69"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -13093,105 +13601,105 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F4064D6-C1ED-1445-98CF-7FC1E20941E1}">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultColWidth="9.77734375" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="6" width="4.109375" customWidth="1"/>
+    <col min="5" max="6" width="4.1640625" customWidth="1"/>
     <col min="7" max="25" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="66"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="65" t="s">
         <v>346</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-    </row>
-    <row r="3" spans="1:25" ht="19.95" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+    </row>
+    <row r="3" spans="1:25" ht="20" customHeight="1">
+      <c r="A3" s="66" t="s">
         <v>347</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="66"/>
+      <c r="Y3" s="66"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -13270,7 +13778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="21.6">
+    <row r="5" spans="1:25" ht="28">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -13305,7 +13813,7 @@
       <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
     </row>
-    <row r="6" spans="1:25" ht="21.6">
+    <row r="6" spans="1:25" ht="28">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -13340,7 +13848,7 @@
       <c r="X6" s="5"/>
       <c r="Y6" s="5"/>
     </row>
-    <row r="7" spans="1:25" ht="21.6">
+    <row r="7" spans="1:25" ht="28">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -13375,7 +13883,7 @@
       <c r="X7" s="5"/>
       <c r="Y7" s="5"/>
     </row>
-    <row r="8" spans="1:25" ht="21.6">
+    <row r="8" spans="1:25" ht="28">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -13410,7 +13918,7 @@
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
     </row>
-    <row r="9" spans="1:25" ht="21.6">
+    <row r="9" spans="1:25" ht="28">
       <c r="A9" s="7">
         <v>5</v>
       </c>
@@ -13445,7 +13953,7 @@
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
     </row>
-    <row r="10" spans="1:25" ht="21.6">
+    <row r="10" spans="1:25" ht="28">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -13480,7 +13988,7 @@
       <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
     </row>
-    <row r="11" spans="1:25" ht="21.6">
+    <row r="11" spans="1:25" ht="28">
       <c r="A11" s="7">
         <v>7</v>
       </c>
@@ -13515,7 +14023,7 @@
       <c r="X11" s="5"/>
       <c r="Y11" s="5"/>
     </row>
-    <row r="12" spans="1:25" ht="21.6">
+    <row r="12" spans="1:25" ht="28">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -13550,7 +14058,7 @@
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
     </row>
-    <row r="13" spans="1:25" ht="21.6">
+    <row r="13" spans="1:25" ht="28">
       <c r="A13" s="7">
         <v>9</v>
       </c>
@@ -13585,7 +14093,7 @@
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
     </row>
-    <row r="14" spans="1:25" ht="21.6">
+    <row r="14" spans="1:25" ht="28">
       <c r="A14" s="7">
         <v>10</v>
       </c>
@@ -13620,7 +14128,7 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
     </row>
-    <row r="15" spans="1:25" ht="21.6">
+    <row r="15" spans="1:25" ht="28">
       <c r="A15" s="7">
         <v>11</v>
       </c>
@@ -13655,7 +14163,7 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
     </row>
-    <row r="16" spans="1:25" ht="21.6">
+    <row r="16" spans="1:25" ht="28">
       <c r="A16" s="7">
         <v>12</v>
       </c>
@@ -13690,7 +14198,7 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
     </row>
-    <row r="17" spans="1:25" ht="21.6">
+    <row r="17" spans="1:25" ht="28">
       <c r="A17" s="7">
         <v>13</v>
       </c>
@@ -13725,7 +14233,7 @@
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
     </row>
-    <row r="18" spans="1:25" ht="21.6">
+    <row r="18" spans="1:25" ht="28">
       <c r="A18" s="7">
         <v>14</v>
       </c>
@@ -13760,7 +14268,7 @@
       <c r="X18" s="5"/>
       <c r="Y18" s="5"/>
     </row>
-    <row r="19" spans="1:25" ht="21.6">
+    <row r="19" spans="1:25" ht="28">
       <c r="A19" s="7">
         <v>15</v>
       </c>
@@ -13795,7 +14303,7 @@
       <c r="X19" s="5"/>
       <c r="Y19" s="5"/>
     </row>
-    <row r="20" spans="1:25" ht="21.6">
+    <row r="20" spans="1:25" ht="28">
       <c r="A20" s="7">
         <v>16</v>
       </c>
@@ -13830,7 +14338,7 @@
       <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
     </row>
-    <row r="21" spans="1:25" ht="21.6">
+    <row r="21" spans="1:25" ht="28">
       <c r="A21" s="7">
         <v>17</v>
       </c>
@@ -13865,7 +14373,7 @@
       <c r="X21" s="5"/>
       <c r="Y21" s="5"/>
     </row>
-    <row r="22" spans="1:25" ht="21.6">
+    <row r="22" spans="1:25" ht="28">
       <c r="A22" s="7">
         <v>18</v>
       </c>
@@ -13900,7 +14408,7 @@
       <c r="X22" s="5"/>
       <c r="Y22" s="5"/>
     </row>
-    <row r="23" spans="1:25" ht="21.6">
+    <row r="23" spans="1:25" ht="28">
       <c r="A23" s="7">
         <v>19</v>
       </c>
@@ -13935,7 +14443,7 @@
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="21.6">
+    <row r="24" spans="1:25" ht="28">
       <c r="A24" s="7">
         <v>20</v>
       </c>
@@ -13970,7 +14478,7 @@
       <c r="X24" s="5"/>
       <c r="Y24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="21.6">
+    <row r="25" spans="1:25" ht="28">
       <c r="A25" s="7">
         <v>21</v>
       </c>
@@ -14005,7 +14513,7 @@
       <c r="X25" s="5"/>
       <c r="Y25" s="5"/>
     </row>
-    <row r="26" spans="1:25" ht="21.6">
+    <row r="26" spans="1:25" ht="28">
       <c r="A26" s="7">
         <v>22</v>
       </c>
@@ -14040,7 +14548,7 @@
       <c r="X26" s="5"/>
       <c r="Y26" s="5"/>
     </row>
-    <row r="27" spans="1:25" ht="21.6">
+    <row r="27" spans="1:25" ht="28">
       <c r="A27" s="7">
         <v>23</v>
       </c>
@@ -14075,7 +14583,7 @@
       <c r="X27" s="5"/>
       <c r="Y27" s="5"/>
     </row>
-    <row r="28" spans="1:25" ht="21.6">
+    <row r="28" spans="1:25" ht="28">
       <c r="A28" s="7">
         <v>24</v>
       </c>
@@ -14110,7 +14618,7 @@
       <c r="X28" s="5"/>
       <c r="Y28" s="5"/>
     </row>
-    <row r="29" spans="1:25" ht="21.6">
+    <row r="29" spans="1:25" ht="28">
       <c r="A29" s="7">
         <v>25</v>
       </c>
@@ -14145,7 +14653,7 @@
       <c r="X29" s="5"/>
       <c r="Y29" s="5"/>
     </row>
-    <row r="30" spans="1:25" ht="21.6">
+    <row r="30" spans="1:25" ht="28">
       <c r="A30" s="7">
         <v>26</v>
       </c>
@@ -14180,7 +14688,7 @@
       <c r="X30" s="5"/>
       <c r="Y30" s="5"/>
     </row>
-    <row r="31" spans="1:25" ht="21.6">
+    <row r="31" spans="1:25" ht="28">
       <c r="A31" s="7">
         <v>27</v>
       </c>
@@ -14215,7 +14723,7 @@
       <c r="X31" s="5"/>
       <c r="Y31" s="5"/>
     </row>
-    <row r="32" spans="1:25" ht="21.6">
+    <row r="32" spans="1:25" ht="28">
       <c r="A32" s="7">
         <v>28</v>
       </c>
@@ -14250,7 +14758,7 @@
       <c r="X32" s="5"/>
       <c r="Y32" s="5"/>
     </row>
-    <row r="33" spans="1:25" ht="21.6">
+    <row r="33" spans="1:25" ht="28">
       <c r="A33" s="7">
         <v>29</v>
       </c>
@@ -14285,7 +14793,7 @@
       <c r="X33" s="5"/>
       <c r="Y33" s="5"/>
     </row>
-    <row r="34" spans="1:25" ht="21.6">
+    <row r="34" spans="1:25" ht="28">
       <c r="A34" s="7">
         <v>30</v>
       </c>
@@ -14320,7 +14828,7 @@
       <c r="X34" s="5"/>
       <c r="Y34" s="5"/>
     </row>
-    <row r="35" spans="1:25" ht="21.6">
+    <row r="35" spans="1:25" ht="28">
       <c r="A35" s="7">
         <v>31</v>
       </c>
@@ -14355,7 +14863,7 @@
       <c r="X35" s="5"/>
       <c r="Y35" s="5"/>
     </row>
-    <row r="36" spans="1:25" ht="21.6">
+    <row r="36" spans="1:25" ht="28">
       <c r="A36" s="7">
         <v>32</v>
       </c>
@@ -14390,7 +14898,7 @@
       <c r="X36" s="5"/>
       <c r="Y36" s="5"/>
     </row>
-    <row r="37" spans="1:25" ht="21.6">
+    <row r="37" spans="1:25" ht="28">
       <c r="A37" s="7">
         <v>33</v>
       </c>
@@ -14425,7 +14933,7 @@
       <c r="X37" s="5"/>
       <c r="Y37" s="5"/>
     </row>
-    <row r="38" spans="1:25" ht="21.6">
+    <row r="38" spans="1:25" ht="28">
       <c r="A38" s="7">
         <v>34</v>
       </c>
@@ -14460,7 +14968,7 @@
       <c r="X38" s="5"/>
       <c r="Y38" s="5"/>
     </row>
-    <row r="39" spans="1:25" ht="21.6">
+    <row r="39" spans="1:25" ht="28">
       <c r="A39" s="7">
         <v>35</v>
       </c>
@@ -14503,108 +15011,109 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181AB12A-43F8-534C-ADCD-AFF80A001E10}">
   <dimension ref="A1:Y36"/>
-  <sheetFormatPr defaultColWidth="9.77734375" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="6" width="4.109375" customWidth="1"/>
+    <col min="5" max="6" width="4.1640625" customWidth="1"/>
     <col min="7" max="25" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="66"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="65" t="s">
         <v>279</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-    </row>
-    <row r="3" spans="1:25" ht="19.95" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+    </row>
+    <row r="3" spans="1:25" ht="20" customHeight="1">
+      <c r="A3" s="66" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="66"/>
+      <c r="Y3" s="66"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -14683,7 +15192,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="21.6">
+    <row r="5" spans="1:25" ht="28">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -14718,7 +15227,7 @@
       <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
     </row>
-    <row r="6" spans="1:25" ht="21.6">
+    <row r="6" spans="1:25" ht="28">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -14753,7 +15262,7 @@
       <c r="X6" s="5"/>
       <c r="Y6" s="5"/>
     </row>
-    <row r="7" spans="1:25" ht="21.6">
+    <row r="7" spans="1:25" ht="28">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -14788,7 +15297,7 @@
       <c r="X7" s="5"/>
       <c r="Y7" s="5"/>
     </row>
-    <row r="8" spans="1:25" ht="21.6">
+    <row r="8" spans="1:25" ht="28">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -14823,7 +15332,7 @@
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
     </row>
-    <row r="9" spans="1:25" ht="21.6">
+    <row r="9" spans="1:25" ht="28">
       <c r="A9" s="7">
         <v>5</v>
       </c>
@@ -14858,7 +15367,7 @@
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
     </row>
-    <row r="10" spans="1:25" ht="21.6">
+    <row r="10" spans="1:25" ht="28">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -14893,7 +15402,7 @@
       <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
     </row>
-    <row r="11" spans="1:25" ht="21.6">
+    <row r="11" spans="1:25" ht="28">
       <c r="A11" s="7">
         <v>7</v>
       </c>
@@ -14928,7 +15437,7 @@
       <c r="X11" s="5"/>
       <c r="Y11" s="5"/>
     </row>
-    <row r="12" spans="1:25" ht="21.6">
+    <row r="12" spans="1:25" ht="28">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -14963,7 +15472,7 @@
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
     </row>
-    <row r="13" spans="1:25" ht="21.6">
+    <row r="13" spans="1:25" ht="28">
       <c r="A13" s="7">
         <v>9</v>
       </c>
@@ -14998,7 +15507,7 @@
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
     </row>
-    <row r="14" spans="1:25" ht="21.6">
+    <row r="14" spans="1:25" ht="28">
       <c r="A14" s="7">
         <v>10</v>
       </c>
@@ -15033,7 +15542,7 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
     </row>
-    <row r="15" spans="1:25" ht="21.6">
+    <row r="15" spans="1:25" ht="28">
       <c r="A15" s="7">
         <v>11</v>
       </c>
@@ -15068,7 +15577,7 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
     </row>
-    <row r="16" spans="1:25" ht="21.6">
+    <row r="16" spans="1:25" ht="28">
       <c r="A16" s="7">
         <v>12</v>
       </c>
@@ -15103,7 +15612,7 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
     </row>
-    <row r="17" spans="1:25" ht="21.6">
+    <row r="17" spans="1:25" ht="28">
       <c r="A17" s="7">
         <v>13</v>
       </c>
@@ -15138,7 +15647,7 @@
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
     </row>
-    <row r="18" spans="1:25" ht="21.6">
+    <row r="18" spans="1:25" ht="28">
       <c r="A18" s="7">
         <v>14</v>
       </c>
@@ -15173,7 +15682,7 @@
       <c r="X18" s="5"/>
       <c r="Y18" s="5"/>
     </row>
-    <row r="19" spans="1:25" ht="21.6">
+    <row r="19" spans="1:25" ht="28">
       <c r="A19" s="7">
         <v>15</v>
       </c>
@@ -15208,7 +15717,7 @@
       <c r="X19" s="5"/>
       <c r="Y19" s="5"/>
     </row>
-    <row r="20" spans="1:25" ht="21.6">
+    <row r="20" spans="1:25" ht="28">
       <c r="A20" s="7">
         <v>16</v>
       </c>
@@ -15243,7 +15752,7 @@
       <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
     </row>
-    <row r="21" spans="1:25" ht="21.6">
+    <row r="21" spans="1:25" ht="28">
       <c r="A21" s="7">
         <v>17</v>
       </c>
@@ -15278,7 +15787,7 @@
       <c r="X21" s="5"/>
       <c r="Y21" s="5"/>
     </row>
-    <row r="22" spans="1:25" ht="21.6">
+    <row r="22" spans="1:25" ht="28">
       <c r="A22" s="7">
         <v>18</v>
       </c>
@@ -15313,7 +15822,7 @@
       <c r="X22" s="5"/>
       <c r="Y22" s="5"/>
     </row>
-    <row r="23" spans="1:25" ht="21.6">
+    <row r="23" spans="1:25" ht="28">
       <c r="A23" s="7">
         <v>19</v>
       </c>
@@ -15348,7 +15857,7 @@
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="21.6">
+    <row r="24" spans="1:25" ht="28">
       <c r="A24" s="7">
         <v>20</v>
       </c>
@@ -15383,7 +15892,7 @@
       <c r="X24" s="5"/>
       <c r="Y24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="21.6">
+    <row r="25" spans="1:25" ht="28">
       <c r="A25" s="7">
         <v>21</v>
       </c>
@@ -15418,7 +15927,7 @@
       <c r="X25" s="5"/>
       <c r="Y25" s="5"/>
     </row>
-    <row r="26" spans="1:25" ht="21.6">
+    <row r="26" spans="1:25" ht="28">
       <c r="A26" s="7">
         <v>22</v>
       </c>
@@ -15453,7 +15962,7 @@
       <c r="X26" s="5"/>
       <c r="Y26" s="5"/>
     </row>
-    <row r="27" spans="1:25" ht="21.6">
+    <row r="27" spans="1:25" ht="28">
       <c r="A27" s="7">
         <v>23</v>
       </c>
@@ -15488,7 +15997,7 @@
       <c r="X27" s="5"/>
       <c r="Y27" s="5"/>
     </row>
-    <row r="28" spans="1:25" ht="21.6">
+    <row r="28" spans="1:25" ht="28">
       <c r="A28" s="7">
         <v>24</v>
       </c>
@@ -15523,7 +16032,7 @@
       <c r="X28" s="5"/>
       <c r="Y28" s="5"/>
     </row>
-    <row r="29" spans="1:25" ht="21.6">
+    <row r="29" spans="1:25" ht="28">
       <c r="A29" s="7">
         <v>25</v>
       </c>
@@ -15558,7 +16067,7 @@
       <c r="X29" s="5"/>
       <c r="Y29" s="5"/>
     </row>
-    <row r="30" spans="1:25" ht="21.6">
+    <row r="30" spans="1:25" ht="28">
       <c r="A30" s="7">
         <v>26</v>
       </c>
@@ -15593,7 +16102,7 @@
       <c r="X30" s="5"/>
       <c r="Y30" s="5"/>
     </row>
-    <row r="31" spans="1:25" ht="21.6">
+    <row r="31" spans="1:25" ht="28">
       <c r="A31" s="7">
         <v>27</v>
       </c>
@@ -15628,7 +16137,7 @@
       <c r="X31" s="5"/>
       <c r="Y31" s="5"/>
     </row>
-    <row r="32" spans="1:25" ht="21.6">
+    <row r="32" spans="1:25" ht="28">
       <c r="A32" s="7">
         <v>28</v>
       </c>
@@ -15663,7 +16172,7 @@
       <c r="X32" s="5"/>
       <c r="Y32" s="5"/>
     </row>
-    <row r="33" spans="1:25" ht="21.6">
+    <row r="33" spans="1:25" ht="28">
       <c r="A33" s="7">
         <v>29</v>
       </c>
@@ -15698,7 +16207,7 @@
       <c r="X33" s="5"/>
       <c r="Y33" s="5"/>
     </row>
-    <row r="34" spans="1:25" ht="21.6">
+    <row r="34" spans="1:25" ht="28">
       <c r="A34" s="7">
         <v>30</v>
       </c>
@@ -15733,7 +16242,7 @@
       <c r="X34" s="5"/>
       <c r="Y34" s="5"/>
     </row>
-    <row r="35" spans="1:25" ht="21.6">
+    <row r="35" spans="1:25" ht="28">
       <c r="A35" s="7">
         <v>31</v>
       </c>
@@ -15768,7 +16277,7 @@
       <c r="X35" s="5"/>
       <c r="Y35" s="5"/>
     </row>
-    <row r="36" spans="1:25" ht="21.6">
+    <row r="36" spans="1:25" ht="28">
       <c r="A36" s="7">
         <v>32</v>
       </c>
@@ -15811,584 +16320,585 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59133ACC-6556-D947-8D3D-C348D695BBC1}">
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="6.77734375" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="6.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5" style="55" customWidth="1"/>
-    <col min="2" max="2" width="3.88671875" style="55" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="55" customWidth="1"/>
-    <col min="4" max="4" width="8.77734375" style="55" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="55" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="55" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" style="55" customWidth="1"/>
-    <col min="8" max="8" width="83.33203125" style="55" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" style="55" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" style="55" customWidth="1"/>
-    <col min="11" max="16384" width="6.77734375" style="55"/>
+    <col min="1" max="1" width="5" style="54" customWidth="1"/>
+    <col min="2" max="2" width="3.83203125" style="54" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="54" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="54" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="54" customWidth="1"/>
+    <col min="8" max="8" width="83.33203125" style="54" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="54" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" style="54" customWidth="1"/>
+    <col min="11" max="16384" width="6.83203125" style="54"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>1171</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="52" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="52" t="s">
         <v>420</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="52" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="52" t="s">
         <v>773</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="52" t="s">
         <v>773</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="52" t="s">
         <v>773</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="53" t="s">
         <v>1172</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="55">
+      <c r="A2" s="54">
         <v>1</v>
       </c>
-      <c r="B2" s="54">
+      <c r="B2" s="53">
         <v>4</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="53" t="s">
         <v>410</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="53" t="s">
         <v>354</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="53" t="s">
         <v>349</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="53" t="s">
         <v>406</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="53" t="s">
         <v>1187</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="55">
+      <c r="A3" s="54">
         <v>2</v>
       </c>
-      <c r="B3" s="54">
+      <c r="B3" s="53">
         <v>4</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="53" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="53" t="s">
         <v>412</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="53" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="54" t="s">
+      <c r="G3" s="53" t="s">
         <v>358</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="53" t="s">
         <v>1186</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="55">
+      <c r="A4" s="54">
         <v>3</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B4" s="53">
         <v>4</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>374</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="53" t="s">
         <v>376</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="53" t="s">
         <v>380</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="G4" s="53" t="s">
         <v>404</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="53" t="s">
         <v>1188</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="55">
+      <c r="A5" s="54">
         <v>4</v>
       </c>
-      <c r="B5" s="54">
+      <c r="B5" s="53">
         <v>4</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>386</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="53" t="s">
         <v>352</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="53" t="s">
         <v>402</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="53" t="s">
         <v>1194</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="55">
+      <c r="A6" s="54">
         <v>5</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="53">
         <v>4</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="53" t="s">
         <v>388</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="53" t="s">
         <v>362</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="53" t="s">
         <v>418</v>
       </c>
-      <c r="G6" s="54" t="s">
+      <c r="G6" s="53" t="s">
         <v>360</v>
       </c>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="53" t="s">
         <v>1189</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="55">
+      <c r="A7" s="54">
         <v>6</v>
       </c>
-      <c r="B7" s="54">
+      <c r="B7" s="53">
         <v>4</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="53" t="s">
         <v>390</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="53" t="s">
         <v>370</v>
       </c>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="53" t="s">
         <v>394</v>
       </c>
-      <c r="G7" s="54" t="s">
+      <c r="G7" s="53" t="s">
         <v>382</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="53" t="s">
         <v>1190</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="55">
+      <c r="A8" s="54">
         <v>7</v>
       </c>
-      <c r="B8" s="54">
+      <c r="B8" s="53">
         <v>4</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>398</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="E8" s="54" t="s">
+      <c r="E8" s="53" t="s">
         <v>396</v>
       </c>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="53" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="54" t="s">
+      <c r="G8" s="53" t="s">
         <v>775</v>
       </c>
-      <c r="H8" s="54" t="s">
+      <c r="H8" s="53" t="s">
         <v>1191</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="55">
+      <c r="A9" s="54">
         <v>8</v>
       </c>
-      <c r="B9" s="54">
+      <c r="B9" s="53">
         <v>3</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="53" t="s">
         <v>392</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="53" t="s">
         <v>414</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="53" t="s">
         <v>416</v>
       </c>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54" t="s">
+      <c r="G9" s="53"/>
+      <c r="H9" s="53" t="s">
         <v>1192</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="55">
+      <c r="A10" s="54">
         <v>9</v>
       </c>
-      <c r="B10" s="54">
+      <c r="B10" s="53">
         <v>3</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="53" t="s">
         <v>781</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="53" t="s">
         <v>777</v>
       </c>
-      <c r="E10" s="54" t="s">
+      <c r="E10" s="53" t="s">
         <v>780</v>
       </c>
-      <c r="F10" s="54" t="s">
+      <c r="F10" s="53" t="s">
         <v>779</v>
       </c>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54" t="s">
+      <c r="G10" s="53"/>
+      <c r="H10" s="53" t="s">
         <v>1193</v>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="54" t="s">
         <v>1171</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="52" t="s">
         <v>421</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="52" t="s">
         <v>420</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="52" t="s">
         <v>422</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="52" t="s">
         <v>773</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="52" t="s">
         <v>773</v>
       </c>
-      <c r="G12" s="53" t="s">
+      <c r="G12" s="52" t="s">
         <v>773</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="H12" s="53" t="s">
         <v>1172</v>
       </c>
-      <c r="I12" s="72" t="s">
+      <c r="I12" s="70" t="s">
         <v>1185</v>
       </c>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="55">
+      <c r="A13" s="54">
         <v>1</v>
       </c>
-      <c r="B13" s="54">
+      <c r="B13" s="53">
         <v>5</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="53" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E13" s="54" t="s">
+      <c r="E13" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="F13" s="54" t="s">
+      <c r="F13" s="53" t="s">
         <v>315</v>
       </c>
-      <c r="G13" s="54" t="s">
+      <c r="G13" s="53" t="s">
         <v>1180</v>
       </c>
-      <c r="H13" s="54" t="s">
+      <c r="H13" s="53" t="s">
         <v>1182</v>
       </c>
-      <c r="I13" s="55">
+      <c r="I13" s="54">
         <v>4</v>
       </c>
-      <c r="J13" s="54" t="s">
+      <c r="J13" s="53" t="s">
         <v>287</v>
       </c>
-      <c r="K13" s="54" t="s">
+      <c r="K13" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="L13" s="54" t="s">
+      <c r="L13" s="53" t="s">
         <v>315</v>
       </c>
-      <c r="M13" s="55" t="s">
+      <c r="M13" s="54" t="s">
         <v>1181</v>
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="55">
+      <c r="A14" s="54">
         <v>2</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="53">
         <v>3</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C14" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="53" t="s">
         <v>1170</v>
       </c>
-      <c r="E14" s="54" t="s">
+      <c r="E14" s="53" t="s">
         <v>309</v>
       </c>
-      <c r="F14" s="54" t="s">
+      <c r="F14" s="53" t="s">
         <v>305</v>
       </c>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54" t="s">
+      <c r="G14" s="53"/>
+      <c r="H14" s="53" t="s">
         <v>1184</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="55">
+      <c r="A15" s="54">
         <v>3</v>
       </c>
-      <c r="B15" s="54">
+      <c r="B15" s="53">
         <v>4</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="53" t="s">
         <v>299</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E15" s="54" t="s">
+      <c r="E15" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="F15" s="54" t="s">
+      <c r="F15" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="G15" s="54" t="s">
+      <c r="G15" s="53" t="s">
         <v>303</v>
       </c>
-      <c r="H15" s="54" t="s">
+      <c r="H15" s="53" t="s">
         <v>1183</v>
       </c>
-      <c r="I15" s="55">
+      <c r="I15" s="54">
         <v>2</v>
       </c>
-      <c r="J15" s="54" t="s">
+      <c r="J15" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="K15" s="54" t="s">
+      <c r="K15" s="53" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="55">
+      <c r="A16" s="54">
         <v>4</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="53">
         <v>4</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="53" t="s">
         <v>317</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E16" s="54" t="s">
+      <c r="E16" s="53" t="s">
         <v>323</v>
       </c>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="53" t="s">
         <v>307</v>
       </c>
-      <c r="G16" s="54" t="s">
+      <c r="G16" s="53" t="s">
         <v>343</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="53" t="s">
         <v>1174</v>
       </c>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="55">
+      <c r="A17" s="54">
         <v>5</v>
       </c>
-      <c r="B17" s="54">
+      <c r="B17" s="53">
         <v>4</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E17" s="54" t="s">
+      <c r="E17" s="53" t="s">
         <v>327</v>
       </c>
-      <c r="F17" s="54" t="s">
+      <c r="F17" s="53" t="s">
         <v>295</v>
       </c>
-      <c r="G17" s="54" t="s">
+      <c r="G17" s="53" t="s">
         <v>345</v>
       </c>
-      <c r="H17" s="54" t="s">
+      <c r="H17" s="53" t="s">
         <v>1173</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="55">
+      <c r="A18" s="54">
         <v>6</v>
       </c>
-      <c r="B18" s="54">
+      <c r="B18" s="53">
         <v>4</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="53" t="s">
         <v>339</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E18" s="54" t="s">
+      <c r="E18" s="53" t="s">
         <v>301</v>
       </c>
-      <c r="F18" s="54" t="s">
+      <c r="F18" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="G18" s="54" t="s">
+      <c r="G18" s="53" t="s">
         <v>313</v>
       </c>
-      <c r="H18" s="54" t="s">
+      <c r="H18" s="53" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="55">
+      <c r="A19" s="54">
         <v>7</v>
       </c>
-      <c r="B19" s="54">
+      <c r="B19" s="53">
         <v>4</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="53" t="s">
         <v>331</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E19" s="54" t="s">
+      <c r="E19" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="F19" s="54" t="s">
+      <c r="F19" s="53" t="s">
         <v>311</v>
       </c>
-      <c r="G19" s="54" t="s">
+      <c r="G19" s="53" t="s">
         <v>1176</v>
       </c>
-      <c r="H19" s="54" t="s">
+      <c r="H19" s="53" t="s">
         <v>1177</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="55">
+      <c r="A20" s="54">
         <v>8</v>
       </c>
-      <c r="B20" s="54">
+      <c r="B20" s="53">
         <v>2</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="53" t="s">
         <v>282</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="D20" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E20" s="54" t="s">
+      <c r="E20" s="53" t="s">
         <v>341</v>
       </c>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54" t="s">
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53" t="s">
         <v>1178</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="55">
+      <c r="A21" s="54">
         <v>9</v>
       </c>
-      <c r="B21" s="54">
+      <c r="B21" s="53">
         <v>1</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="53" t="s">
         <v>335</v>
       </c>
-      <c r="D21" s="54" t="s">
+      <c r="D21" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="55" t="s">
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="54" t="s">
         <v>1179</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="B23" s="54">
+      <c r="B23" s="53">
         <f>SUM(B13:B21)</f>
         <v>31</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="54" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="19.2">
-      <c r="B32" s="56" t="s">
+    <row r="32" spans="1:8" ht="17">
+      <c r="B32" s="55" t="s">
         <v>778</v>
       </c>
     </row>
@@ -16398,27 +16908,29 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7750C4B5-9B55-CC4B-9482-D16EB774F919}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
-  <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7750C4B5-9B55-CC4B-9482-D16EB774F919}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90659A0F-F212-F044-BE56-4EC7AB740CAC}">
   <dimension ref="A1:B74"/>
-  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="25.109375" style="17" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" style="17" customWidth="1"/>
     <col min="2" max="2" width="19" style="17" customWidth="1"/>
-    <col min="3" max="16384" width="10.77734375" style="17"/>
+    <col min="3" max="16384" width="10.83203125" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -17012,13 +17524,14 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A84614CC-9406-C446-8F8F-B5A5631DB511}">
   <dimension ref="A1:B69"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -17582,22 +18095,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BEDD6E-3D2A-A340-890A-FAE6803B46D9}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" style="26" customWidth="1"/>
-    <col min="4" max="6" width="10.77734375" style="26"/>
-    <col min="7" max="7" width="13.77734375" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" style="25" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="26" customWidth="1"/>
+    <col min="3" max="3" width="6.5" style="26" customWidth="1"/>
+    <col min="4" max="6" width="10.83203125" style="26"/>
+    <col min="7" max="7" width="13.83203125" style="26" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" style="26" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="49.6640625" style="23" customWidth="1"/>
     <col min="10" max="11" width="0" style="26" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="6.33203125" style="26" hidden="1" customWidth="1"/>
-    <col min="13" max="15" width="20.77734375" style="26" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="0.109375" style="26" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.44140625" style="26" customWidth="1"/>
-    <col min="18" max="18" width="21.109375" style="26" customWidth="1"/>
-    <col min="19" max="16384" width="10.77734375" style="26"/>
+    <col min="13" max="15" width="20.83203125" style="26" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="0.1640625" style="26" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5" style="26" customWidth="1"/>
+    <col min="18" max="18" width="21.1640625" style="26" customWidth="1"/>
+    <col min="19" max="16384" width="10.83203125" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -17625,7 +18138,7 @@
       <c r="H1" s="31" t="s">
         <v>424</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="48" t="s">
         <v>785</v>
       </c>
       <c r="J1" s="32" t="s">
@@ -17656,7 +18169,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="27.6">
+    <row r="2" spans="1:18">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -17679,7 +18192,7 @@
         <v>500</v>
       </c>
       <c r="H2" s="35"/>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="47" t="s">
         <v>793</v>
       </c>
       <c r="J2" s="36">
@@ -17731,7 +18244,7 @@
         <v>504</v>
       </c>
       <c r="H3" s="35"/>
-      <c r="I3" s="50"/>
+      <c r="I3" s="49"/>
       <c r="J3" s="36"/>
       <c r="K3" s="36"/>
       <c r="L3" s="36"/>
@@ -17761,7 +18274,7 @@
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="50"/>
+      <c r="I4" s="49"/>
       <c r="J4" s="36"/>
       <c r="K4" s="36"/>
       <c r="L4" s="36"/>
@@ -17772,7 +18285,7 @@
       <c r="Q4" s="36"/>
       <c r="R4" s="38"/>
     </row>
-    <row r="5" spans="1:18" ht="27.6">
+    <row r="5" spans="1:18" ht="32">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -17795,7 +18308,7 @@
         <v>509</v>
       </c>
       <c r="H5" s="35"/>
-      <c r="I5" s="48" t="s">
+      <c r="I5" s="47" t="s">
         <v>799</v>
       </c>
       <c r="J5" s="36">
@@ -17822,7 +18335,7 @@
       <c r="Q5" s="36"/>
       <c r="R5" s="38"/>
     </row>
-    <row r="6" spans="1:18" ht="27.6">
+    <row r="6" spans="1:18">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -17843,7 +18356,7 @@
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="35"/>
-      <c r="I6" s="48" t="s">
+      <c r="I6" s="47" t="s">
         <v>805</v>
       </c>
       <c r="J6" s="36">
@@ -17872,7 +18385,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="19.05" customHeight="1">
+    <row r="7" spans="1:18" ht="19" customHeight="1">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -17895,7 +18408,7 @@
         <v>515</v>
       </c>
       <c r="H7" s="35"/>
-      <c r="I7" s="48" t="s">
+      <c r="I7" s="47" t="s">
         <v>811</v>
       </c>
       <c r="J7" s="36">
@@ -17945,7 +18458,7 @@
       </c>
       <c r="G8" s="35"/>
       <c r="H8" s="35"/>
-      <c r="I8" s="48" t="s">
+      <c r="I8" s="47" t="s">
         <v>817</v>
       </c>
       <c r="J8" s="36">
@@ -17972,7 +18485,7 @@
       <c r="Q8" s="36"/>
       <c r="R8" s="38"/>
     </row>
-    <row r="9" spans="1:18" ht="55.2">
+    <row r="9" spans="1:18" ht="64">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -17993,7 +18506,7 @@
       </c>
       <c r="G9" s="35"/>
       <c r="H9" s="35"/>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="47" t="s">
         <v>823</v>
       </c>
       <c r="J9" s="36">
@@ -18045,7 +18558,7 @@
         <v>525</v>
       </c>
       <c r="H10" s="35"/>
-      <c r="I10" s="48" t="s">
+      <c r="I10" s="47" t="s">
         <v>829</v>
       </c>
       <c r="J10" s="36">
@@ -18095,7 +18608,7 @@
         <v>529</v>
       </c>
       <c r="H11" s="35"/>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="47" t="s">
         <v>835</v>
       </c>
       <c r="J11" s="36">
@@ -18147,7 +18660,7 @@
         <v>532</v>
       </c>
       <c r="H12" s="35"/>
-      <c r="I12" s="51"/>
+      <c r="I12" s="50"/>
       <c r="J12" s="36"/>
       <c r="K12" s="36"/>
       <c r="L12" s="36"/>
@@ -18183,7 +18696,7 @@
         <v>536</v>
       </c>
       <c r="H13" s="35"/>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="47" t="s">
         <v>841</v>
       </c>
       <c r="J13" s="36">
@@ -18212,7 +18725,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="27.6">
+    <row r="14" spans="1:18" ht="32">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -18235,7 +18748,7 @@
         <v>540</v>
       </c>
       <c r="H14" s="35"/>
-      <c r="I14" s="48" t="s">
+      <c r="I14" s="47" t="s">
         <v>846</v>
       </c>
       <c r="J14" s="36">
@@ -18264,7 +18777,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="27.6">
+    <row r="15" spans="1:18">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -18287,7 +18800,7 @@
         <v>544</v>
       </c>
       <c r="H15" s="35"/>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="47" t="s">
         <v>851</v>
       </c>
       <c r="J15" s="36">
@@ -18337,7 +18850,7 @@
       <c r="H16" s="35" t="s">
         <v>428</v>
       </c>
-      <c r="I16" s="50"/>
+      <c r="I16" s="49"/>
       <c r="J16" s="36"/>
       <c r="K16" s="36"/>
       <c r="L16" s="36"/>
@@ -18348,7 +18861,7 @@
       <c r="Q16" s="36"/>
       <c r="R16" s="38"/>
     </row>
-    <row r="17" spans="1:18" ht="55.2">
+    <row r="17" spans="1:18" ht="64">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -18371,7 +18884,7 @@
         <v>548</v>
       </c>
       <c r="H17" s="35"/>
-      <c r="I17" s="48" t="s">
+      <c r="I17" s="47" t="s">
         <v>857</v>
       </c>
       <c r="J17" s="36">
@@ -18421,7 +18934,7 @@
       </c>
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
-      <c r="I18" s="52" t="s">
+      <c r="I18" s="51" t="s">
         <v>863</v>
       </c>
       <c r="J18" s="43">
@@ -18482,7 +18995,7 @@
       <c r="H24" s="35" t="s">
         <v>424</v>
       </c>
-      <c r="I24" s="48" t="s">
+      <c r="I24" s="47" t="s">
         <v>785</v>
       </c>
       <c r="J24" s="36" t="s">
@@ -18513,7 +19026,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="27.6">
+    <row r="25" spans="1:18" ht="32">
       <c r="A25" s="35">
         <v>1</v>
       </c>
@@ -18536,7 +19049,7 @@
         <v>434</v>
       </c>
       <c r="H25" s="35"/>
-      <c r="I25" s="48" t="s">
+      <c r="I25" s="47" t="s">
         <v>869</v>
       </c>
       <c r="J25" s="36">
@@ -18565,7 +19078,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="41.4">
+    <row r="26" spans="1:18" ht="48">
       <c r="A26" s="35">
         <v>2</v>
       </c>
@@ -18586,7 +19099,7 @@
       </c>
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
-      <c r="I26" s="48" t="s">
+      <c r="I26" s="47" t="s">
         <v>875</v>
       </c>
       <c r="J26" s="36">
@@ -18615,7 +19128,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="27.6">
+    <row r="27" spans="1:18" ht="32">
       <c r="A27" s="35">
         <v>3</v>
       </c>
@@ -18636,7 +19149,7 @@
       </c>
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
-      <c r="I27" s="48" t="s">
+      <c r="I27" s="47" t="s">
         <v>881</v>
       </c>
       <c r="J27" s="36">
@@ -18665,7 +19178,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="41.4">
+    <row r="28" spans="1:18" ht="48">
       <c r="A28" s="35">
         <v>4</v>
       </c>
@@ -18688,7 +19201,7 @@
         <v>444</v>
       </c>
       <c r="H28" s="35"/>
-      <c r="I28" s="48" t="s">
+      <c r="I28" s="47" t="s">
         <v>887</v>
       </c>
       <c r="J28" s="36">
@@ -18738,7 +19251,7 @@
         <v>448</v>
       </c>
       <c r="H29" s="35"/>
-      <c r="I29" s="48" t="s">
+      <c r="I29" s="47" t="s">
         <v>893</v>
       </c>
       <c r="J29" s="36">
@@ -18767,7 +19280,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="27.6">
+    <row r="30" spans="1:18" ht="32">
       <c r="A30" s="35">
         <v>6</v>
       </c>
@@ -18790,7 +19303,7 @@
         <v>454</v>
       </c>
       <c r="H30" s="35"/>
-      <c r="I30" s="48" t="s">
+      <c r="I30" s="47" t="s">
         <v>899</v>
       </c>
       <c r="J30" s="36">
@@ -18840,7 +19353,7 @@
         <v>458</v>
       </c>
       <c r="H31" s="35"/>
-      <c r="I31" s="48" t="s">
+      <c r="I31" s="47" t="s">
         <v>905</v>
       </c>
       <c r="J31" s="36">
@@ -18869,7 +19382,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="27.6">
+    <row r="32" spans="1:18" ht="32">
       <c r="A32" s="35">
         <v>8</v>
       </c>
@@ -18892,7 +19405,7 @@
         <v>462</v>
       </c>
       <c r="H32" s="35"/>
-      <c r="I32" s="48" t="s">
+      <c r="I32" s="47" t="s">
         <v>911</v>
       </c>
       <c r="J32" s="36">
@@ -18944,7 +19457,7 @@
         <v>483</v>
       </c>
       <c r="H33" s="35"/>
-      <c r="I33" s="48" t="s">
+      <c r="I33" s="47" t="s">
         <v>922</v>
       </c>
       <c r="J33" s="36">
@@ -18975,7 +19488,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="27.6">
+    <row r="34" spans="1:18" ht="32">
       <c r="A34" s="35">
         <v>10</v>
       </c>
@@ -18998,7 +19511,7 @@
         <v>467</v>
       </c>
       <c r="H34" s="35"/>
-      <c r="I34" s="48" t="s">
+      <c r="I34" s="47" t="s">
         <v>970</v>
       </c>
       <c r="J34" s="36">
@@ -19050,7 +19563,7 @@
         <v>471</v>
       </c>
       <c r="H35" s="35"/>
-      <c r="I35" s="48" t="s">
+      <c r="I35" s="47" t="s">
         <v>964</v>
       </c>
       <c r="J35" s="36">
@@ -19081,7 +19594,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="27.6">
+    <row r="36" spans="1:18" ht="32">
       <c r="A36" s="35">
         <v>12</v>
       </c>
@@ -19104,7 +19617,7 @@
         <v>475</v>
       </c>
       <c r="H36" s="36"/>
-      <c r="I36" s="48" t="s">
+      <c r="I36" s="47" t="s">
         <v>958</v>
       </c>
       <c r="J36" s="36">
@@ -19131,7 +19644,7 @@
       <c r="Q36" s="36"/>
       <c r="R36" s="40"/>
     </row>
-    <row r="37" spans="1:18" ht="41.4">
+    <row r="37" spans="1:18" ht="48">
       <c r="A37" s="35">
         <v>13</v>
       </c>
@@ -19154,7 +19667,7 @@
         <v>479</v>
       </c>
       <c r="H37" s="35"/>
-      <c r="I37" s="48" t="s">
+      <c r="I37" s="47" t="s">
         <v>952</v>
       </c>
       <c r="J37" s="36">
@@ -19183,7 +19696,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="41.4">
+    <row r="38" spans="1:18" ht="48">
       <c r="A38" s="35">
         <v>14</v>
       </c>
@@ -19206,7 +19719,7 @@
         <v>772</v>
       </c>
       <c r="H38" s="35"/>
-      <c r="I38" s="48" t="s">
+      <c r="I38" s="47" t="s">
         <v>946</v>
       </c>
       <c r="J38" s="36">
@@ -19258,7 +19771,7 @@
         <v>487</v>
       </c>
       <c r="H39" s="35"/>
-      <c r="I39" s="48" t="s">
+      <c r="I39" s="47" t="s">
         <v>940</v>
       </c>
       <c r="J39" s="36">
@@ -19282,7 +19795,7 @@
       <c r="P39" s="36" t="s">
         <v>935</v>
       </c>
-      <c r="Q39" s="47"/>
+      <c r="Q39" s="36"/>
       <c r="R39" s="40"/>
     </row>
     <row r="40" spans="1:18">
@@ -19308,7 +19821,7 @@
         <v>491</v>
       </c>
       <c r="H40" s="35"/>
-      <c r="I40" s="48" t="s">
+      <c r="I40" s="47" t="s">
         <v>934</v>
       </c>
       <c r="J40" s="36">
@@ -19332,10 +19845,10 @@
       <c r="P40" s="36" t="s">
         <v>929</v>
       </c>
-      <c r="Q40" s="47"/>
+      <c r="Q40" s="36"/>
       <c r="R40" s="40"/>
     </row>
-    <row r="41" spans="1:18" ht="41.4">
+    <row r="41" spans="1:18" ht="48">
       <c r="A41" s="35">
         <v>17</v>
       </c>
@@ -19358,7 +19871,7 @@
         <v>495</v>
       </c>
       <c r="H41" s="35"/>
-      <c r="I41" s="48" t="s">
+      <c r="I41" s="47" t="s">
         <v>928</v>
       </c>
       <c r="J41" s="36">
@@ -19402,23 +19915,863 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{890DB625-7870-104E-BF01-8B91488CC203}">
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="71" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="35" t="s">
+        <v>783</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16">
+      <c r="A4" s="35">
+        <v>1</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>496</v>
+      </c>
+      <c r="C4" s="35">
+        <v>4</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>498</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>499</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16">
+      <c r="A5" s="35">
+        <v>2</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="35">
+        <v>4</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>502</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>503</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16">
+      <c r="A6" s="35">
+        <v>3</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="35">
+        <v>1</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+    </row>
+    <row r="7" spans="1:7" ht="16">
+      <c r="A7" s="35">
+        <v>4</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>506</v>
+      </c>
+      <c r="C7" s="35">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>507</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>508</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16">
+      <c r="A8" s="35">
+        <v>5</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>510</v>
+      </c>
+      <c r="C8" s="35">
+        <v>3</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>511</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>512</v>
+      </c>
+      <c r="G8" s="35"/>
+    </row>
+    <row r="9" spans="1:7" ht="16">
+      <c r="A9" s="35">
+        <v>6</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>513</v>
+      </c>
+      <c r="C9" s="35">
+        <v>5</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>514</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16">
+      <c r="A10" s="35">
+        <v>7</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="C10" s="35">
+        <v>3</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="G10" s="35"/>
+    </row>
+    <row r="11" spans="1:7" ht="16">
+      <c r="A11" s="35">
+        <v>8</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C11" s="35">
+        <v>3</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>521</v>
+      </c>
+      <c r="G11" s="35"/>
+    </row>
+    <row r="12" spans="1:7" ht="16">
+      <c r="A12" s="35">
+        <v>9</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="C12" s="35">
+        <v>4</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>524</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16">
+      <c r="A13" s="35">
+        <v>10</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="C13" s="35">
+        <v>4</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16">
+      <c r="A14" s="35">
+        <v>11</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>530</v>
+      </c>
+      <c r="C14" s="35">
+        <v>4</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>531</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16">
+      <c r="A15" s="35">
+        <v>12</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>533</v>
+      </c>
+      <c r="C15" s="35">
+        <v>4</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>534</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>535</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16">
+      <c r="A16" s="35">
+        <v>13</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>537</v>
+      </c>
+      <c r="C16" s="35">
+        <v>4</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16">
+      <c r="A17" s="35">
+        <v>14</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>541</v>
+      </c>
+      <c r="C17" s="35">
+        <v>4</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>542</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>543</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16">
+      <c r="A18" s="35">
+        <v>15</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>552</v>
+      </c>
+      <c r="C18" s="35">
+        <v>3</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>553</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>554</v>
+      </c>
+      <c r="G18" s="35"/>
+    </row>
+    <row r="19" spans="1:7" ht="16">
+      <c r="A19" s="35">
+        <v>16</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>545</v>
+      </c>
+      <c r="C19" s="35">
+        <v>4</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>546</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>547</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16">
+      <c r="A20" s="35">
+        <v>17</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="C20" s="35">
+        <v>3</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="G20" s="35"/>
+    </row>
+    <row r="22" spans="1:7" ht="16">
+      <c r="A22" s="35" t="s">
+        <v>783</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16">
+      <c r="A23" s="35">
+        <v>1</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="C23" s="35">
+        <v>5</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="G23" s="35" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16">
+      <c r="A24" s="35">
+        <v>2</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>435</v>
+      </c>
+      <c r="C24" s="35">
+        <v>3</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>437</v>
+      </c>
+      <c r="G24" s="35"/>
+    </row>
+    <row r="25" spans="1:7" ht="16">
+      <c r="A25" s="35">
+        <v>3</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="C25" s="35">
+        <v>3</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>439</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="G25" s="35"/>
+    </row>
+    <row r="26" spans="1:7" ht="16">
+      <c r="A26" s="35">
+        <v>4</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>441</v>
+      </c>
+      <c r="C26" s="35">
+        <v>4</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>442</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>443</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16">
+      <c r="A27" s="35">
+        <v>5</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="C27" s="35">
+        <v>4</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>446</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="G27" s="35" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16">
+      <c r="A28" s="35">
+        <v>6</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="C28" s="35">
+        <v>4</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>452</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>453</v>
+      </c>
+      <c r="G28" s="35" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16">
+      <c r="A29" s="35">
+        <v>7</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="C29" s="35">
+        <v>4</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>456</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>457</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16">
+      <c r="A30" s="35">
+        <v>8</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>459</v>
+      </c>
+      <c r="C30" s="35">
+        <v>4</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>460</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="G30" s="35" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16">
+      <c r="A31" s="35">
+        <v>9</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="35">
+        <v>4</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>450</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>449</v>
+      </c>
+      <c r="G31" s="35" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16">
+      <c r="A32" s="35">
+        <v>10</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>463</v>
+      </c>
+      <c r="C32" s="35">
+        <v>5</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E32" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="G32" s="35" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16">
+      <c r="A33" s="35">
+        <v>11</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="C33" s="35">
+        <v>4</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>469</v>
+      </c>
+      <c r="F33" s="35" t="s">
+        <v>470</v>
+      </c>
+      <c r="G33" s="35" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16">
+      <c r="A34" s="35">
+        <v>12</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="C34" s="35">
+        <v>4</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="G34" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="16">
+      <c r="A35" s="35">
+        <v>13</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="C35" s="35">
+        <v>5</v>
+      </c>
+      <c r="D35" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E35" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F35" s="35" t="s">
+        <v>478</v>
+      </c>
+      <c r="G35" s="35" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="16">
+      <c r="A36" s="35">
+        <v>14</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>480</v>
+      </c>
+      <c r="C36" s="35">
+        <v>5</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>429</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="F36" s="35" t="s">
+        <v>482</v>
+      </c>
+      <c r="G36" s="35" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16">
+      <c r="A37" s="35">
+        <v>15</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>484</v>
+      </c>
+      <c r="C37" s="35">
+        <v>4</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E37" s="35" t="s">
+        <v>485</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16">
+      <c r="A38" s="35">
+        <v>16</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>488</v>
+      </c>
+      <c r="C38" s="35">
+        <v>4</v>
+      </c>
+      <c r="D38" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E38" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="G38" s="35" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="16">
+      <c r="A39" s="35">
+        <v>17</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>492</v>
+      </c>
+      <c r="C39" s="35">
+        <v>4</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>493</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>494</v>
+      </c>
+      <c r="G39" s="35" t="s">
+        <v>495</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA7C430-7738-A84B-BFA9-AD3645C1BF55}">
   <dimension ref="A1:M33"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="6" width="11.44140625" style="21"/>
-    <col min="7" max="7" width="14.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="11.5" style="21"/>
+    <col min="7" max="7" width="14.83203125" style="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="21"/>
+    <col min="9" max="9" width="11.5" style="21"/>
     <col min="10" max="10" width="16" style="21" customWidth="1"/>
-    <col min="11" max="11" width="40.77734375" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" style="21"/>
-    <col min="13" max="13" width="255.77734375" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.44140625" style="21"/>
+    <col min="11" max="11" width="40.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" style="21"/>
+    <col min="13" max="13" width="255.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.5" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -19462,7 +20815,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="17.399999999999999">
+    <row r="2" spans="1:13" ht="22">
       <c r="A2" s="21">
         <v>24</v>
       </c>
@@ -19503,7 +20856,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="17.399999999999999">
+    <row r="3" spans="1:13" ht="22">
       <c r="A3" s="21">
         <v>32</v>
       </c>
@@ -19544,7 +20897,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="17.399999999999999">
+    <row r="4" spans="1:13" ht="22">
       <c r="A4" s="21">
         <v>22</v>
       </c>
@@ -19585,7 +20938,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="17.399999999999999">
+    <row r="5" spans="1:13" ht="22">
       <c r="A5" s="21">
         <v>17</v>
       </c>
@@ -19626,7 +20979,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="17.399999999999999">
+    <row r="6" spans="1:13" ht="22">
       <c r="A6" s="21">
         <v>31</v>
       </c>
@@ -19667,7 +21020,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="17.399999999999999">
+    <row r="7" spans="1:13" ht="22">
       <c r="A7" s="21">
         <v>19</v>
       </c>
@@ -19708,7 +21061,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="17.399999999999999">
+    <row r="8" spans="1:13" ht="22">
       <c r="A8" s="21">
         <v>29</v>
       </c>
@@ -19749,7 +21102,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="17.399999999999999">
+    <row r="9" spans="1:13" ht="22">
       <c r="A9" s="21">
         <v>16</v>
       </c>
@@ -19790,7 +21143,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="17.399999999999999">
+    <row r="10" spans="1:13" ht="22">
       <c r="A10" s="21">
         <v>23</v>
       </c>
@@ -19831,7 +21184,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="17.399999999999999">
+    <row r="11" spans="1:13" ht="22">
       <c r="A11" s="21">
         <v>18</v>
       </c>
@@ -19872,7 +21225,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="17.399999999999999">
+    <row r="12" spans="1:13" ht="22">
       <c r="A12" s="21">
         <v>14</v>
       </c>
@@ -19913,7 +21266,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="17.399999999999999">
+    <row r="13" spans="1:13" ht="22">
       <c r="A13" s="21">
         <v>10</v>
       </c>
@@ -19954,7 +21307,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="17.399999999999999">
+    <row r="14" spans="1:13" ht="22">
       <c r="A14" s="21">
         <v>15</v>
       </c>
@@ -19995,7 +21348,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="17.399999999999999">
+    <row r="15" spans="1:13" ht="22">
       <c r="A15" s="21">
         <v>7</v>
       </c>
@@ -20036,7 +21389,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="17.399999999999999">
+    <row r="16" spans="1:13" ht="22">
       <c r="A16" s="21">
         <v>20</v>
       </c>
@@ -20077,7 +21430,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="17.399999999999999">
+    <row r="17" spans="1:13" ht="22">
       <c r="A17" s="21">
         <v>8</v>
       </c>
@@ -20118,7 +21471,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="17.399999999999999">
+    <row r="18" spans="1:13" ht="22">
       <c r="A18" s="21">
         <v>13</v>
       </c>
@@ -20159,7 +21512,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="17.399999999999999">
+    <row r="19" spans="1:13" ht="22">
       <c r="A19" s="21">
         <v>11</v>
       </c>
@@ -20200,7 +21553,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="17.399999999999999">
+    <row r="20" spans="1:13" ht="22">
       <c r="A20" s="21">
         <v>9</v>
       </c>
@@ -20241,7 +21594,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="17.399999999999999">
+    <row r="21" spans="1:13" ht="22">
       <c r="A21" s="21">
         <v>30</v>
       </c>
@@ -20282,7 +21635,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="17.399999999999999">
+    <row r="22" spans="1:13" ht="22">
       <c r="A22" s="21">
         <v>21</v>
       </c>
@@ -20323,7 +21676,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="17.399999999999999">
+    <row r="23" spans="1:13" ht="22">
       <c r="A23" s="21">
         <v>12</v>
       </c>
@@ -20364,7 +21717,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="17.399999999999999">
+    <row r="24" spans="1:13" ht="22">
       <c r="A24" s="21">
         <v>5</v>
       </c>
@@ -20405,7 +21758,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="17.399999999999999">
+    <row r="25" spans="1:13" ht="22">
       <c r="A25" s="21">
         <v>25</v>
       </c>
@@ -20446,7 +21799,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="17.399999999999999">
+    <row r="26" spans="1:13" ht="22">
       <c r="A26" s="21">
         <v>4</v>
       </c>
@@ -20487,7 +21840,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="17.399999999999999">
+    <row r="27" spans="1:13" ht="22">
       <c r="A27" s="21">
         <v>6</v>
       </c>
@@ -20528,7 +21881,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="17.399999999999999">
+    <row r="28" spans="1:13" ht="22">
       <c r="A28" s="21">
         <v>28</v>
       </c>
@@ -20569,7 +21922,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="17.399999999999999">
+    <row r="29" spans="1:13" ht="22">
       <c r="A29" s="21">
         <v>1</v>
       </c>
@@ -20610,7 +21963,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="17.399999999999999">
+    <row r="30" spans="1:13" ht="22">
       <c r="A30" s="21">
         <v>3</v>
       </c>
@@ -20651,7 +22004,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="17.399999999999999">
+    <row r="31" spans="1:13" ht="22">
       <c r="A31" s="21">
         <v>26</v>
       </c>
@@ -20692,7 +22045,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="17.399999999999999">
+    <row r="32" spans="1:13" ht="22">
       <c r="A32" s="21">
         <v>27</v>
       </c>
@@ -20733,7 +22086,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="17.399999999999999">
+    <row r="33" spans="1:13" ht="22">
       <c r="A33" s="21">
         <v>2</v>
       </c>
@@ -20781,21 +22134,22 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08CA6B99-C27B-4F97-B079-228CC4A6ABC1}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="71.77734375" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="71.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15">
+    <row r="1" spans="1:14" ht="16">
       <c r="A1" s="35" t="s">
         <v>783</v>
       </c>
@@ -20820,26 +22174,26 @@
       <c r="H1" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="I1" s="58" t="s">
+      <c r="I1" s="57" t="s">
         <v>1197</v>
       </c>
-      <c r="J1" s="57" t="s">
+      <c r="J1" s="56" t="s">
         <v>1185</v>
       </c>
-      <c r="K1" s="57" t="s">
+      <c r="K1" s="56" t="s">
         <v>1185</v>
       </c>
-      <c r="L1" s="57" t="s">
+      <c r="L1" s="56" t="s">
         <v>1185</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="M1" s="56" t="s">
         <v>1185</v>
       </c>
-      <c r="N1" s="57" t="s">
+      <c r="N1" s="56" t="s">
         <v>1185</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15">
+    <row r="2" spans="1:14" ht="16">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -20864,7 +22218,7 @@
       <c r="H2" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>1196</v>
       </c>
       <c r="J2">
@@ -20877,7 +22231,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15">
+    <row r="3" spans="1:14" ht="16">
       <c r="A3" s="35">
         <v>2</v>
       </c>
@@ -20900,7 +22254,7 @@
         <v>437</v>
       </c>
       <c r="H3" s="35"/>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="57" t="s">
         <v>1198</v>
       </c>
       <c r="J3">
@@ -20913,7 +22267,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15">
+    <row r="4" spans="1:14" ht="16">
       <c r="A4" s="35">
         <v>3</v>
       </c>
@@ -20936,11 +22290,11 @@
         <v>440</v>
       </c>
       <c r="H4" s="35"/>
-      <c r="I4" s="58" t="s">
+      <c r="I4" s="57" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15">
+    <row r="5" spans="1:14" ht="16">
       <c r="A5" s="35">
         <v>4</v>
       </c>
@@ -20965,11 +22319,11 @@
       <c r="H5" s="35" t="s">
         <v>444</v>
       </c>
-      <c r="I5" s="58" t="s">
+      <c r="I5" s="57" t="s">
         <v>1200</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15">
+    <row r="6" spans="1:14" ht="16">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -20994,11 +22348,11 @@
       <c r="H6" s="35" t="s">
         <v>448</v>
       </c>
-      <c r="I6" s="58" t="s">
+      <c r="I6" s="57" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15">
+    <row r="7" spans="1:14" ht="16">
       <c r="A7" s="35">
         <v>6</v>
       </c>
@@ -21039,7 +22393,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15">
+    <row r="8" spans="1:14" ht="16">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -21064,11 +22418,11 @@
       <c r="H8" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="I8" s="57" t="s">
+      <c r="I8" s="56" t="s">
         <v>1202</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15">
+    <row r="9" spans="1:14" ht="16">
       <c r="A9" s="35">
         <v>8</v>
       </c>
@@ -21093,11 +22447,11 @@
       <c r="H9" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="56" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15">
+    <row r="10" spans="1:14" ht="16">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -21122,11 +22476,11 @@
       <c r="H10" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="I10" s="57" t="s">
+      <c r="I10" s="56" t="s">
         <v>1204</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15">
+    <row r="11" spans="1:14" ht="16">
       <c r="A11" s="35">
         <v>10</v>
       </c>
@@ -21151,11 +22505,11 @@
       <c r="H11" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="I11" s="57" t="s">
+      <c r="I11" s="56" t="s">
         <v>1205</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15">
+    <row r="12" spans="1:14" ht="16">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -21180,17 +22534,17 @@
       <c r="H12" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="I12" s="57" t="s">
+      <c r="I12" s="56" t="s">
         <v>1207</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="59" t="s">
+      <c r="K12" s="25" t="s">
         <v>1206</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15">
+    <row r="13" spans="1:14" ht="16">
       <c r="A13" s="35">
         <v>12</v>
       </c>
@@ -21213,11 +22567,11 @@
       <c r="H13" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="56" t="s">
         <v>1208</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15">
+    <row r="14" spans="1:14" ht="16">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -21242,11 +22596,11 @@
       <c r="H14" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="I14" s="57" t="s">
+      <c r="I14" s="56" t="s">
         <v>1209</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15">
+    <row r="15" spans="1:14" ht="16">
       <c r="A15" s="35">
         <v>14</v>
       </c>
@@ -21269,17 +22623,17 @@
       <c r="H15" s="35" t="s">
         <v>772</v>
       </c>
-      <c r="I15" s="57" t="s">
+      <c r="I15" s="56" t="s">
         <v>1211</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="59" t="s">
+      <c r="K15" s="25" t="s">
         <v>1210</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15">
+    <row r="16" spans="1:14" ht="16">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -21304,17 +22658,17 @@
       <c r="H16" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="I16" s="57" t="s">
+      <c r="I16" s="56" t="s">
         <v>1213</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
-      <c r="K16" s="59" t="s">
+      <c r="K16" s="25" t="s">
         <v>1212</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15">
+    <row r="17" spans="1:12" ht="16">
       <c r="A17" s="35">
         <v>16</v>
       </c>
@@ -21339,7 +22693,7 @@
       <c r="H17" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="I17" s="57" t="s">
+      <c r="I17" s="56" t="s">
         <v>1214</v>
       </c>
       <c r="J17">
@@ -21352,7 +22706,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15">
+    <row r="18" spans="1:12" ht="16">
       <c r="A18" s="35">
         <v>17</v>
       </c>
@@ -21377,7 +22731,7 @@
       <c r="H18" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="I18" s="57" t="s">
+      <c r="I18" s="56" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -21388,20 +22742,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5668750C-27A9-4830-BBCD-A49BEBB03C2E}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" customWidth="1"/>
-    <col min="8" max="8" width="15.77734375" customWidth="1"/>
-    <col min="9" max="9" width="60.88671875" customWidth="1"/>
-    <col min="10" max="10" width="53.88671875" customWidth="1"/>
-    <col min="11" max="11" width="63.21875" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="60.83203125" customWidth="1"/>
+    <col min="10" max="10" width="53.83203125" customWidth="1"/>
+    <col min="11" max="11" width="63.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15">
+    <row r="1" spans="1:14" ht="16">
       <c r="A1" s="35" t="s">
         <v>783</v>
       </c>
@@ -21426,23 +22780,23 @@
       <c r="H1" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="I1" s="58" t="s">
+      <c r="I1" s="57" t="s">
         <v>1197</v>
       </c>
-      <c r="J1" s="58" t="s">
+      <c r="J1" s="57" t="s">
         <v>1249</v>
       </c>
-      <c r="K1" s="58" t="s">
+      <c r="K1" s="57" t="s">
         <v>1286</v>
       </c>
-      <c r="L1" s="58" t="s">
+      <c r="L1" s="57" t="s">
         <v>1251</v>
       </c>
       <c r="M1">
         <v>5.15</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15">
+    <row r="2" spans="1:14" ht="16">
       <c r="A2" s="35">
         <v>6</v>
       </c>
@@ -21467,16 +22821,16 @@
       <c r="H2" s="35" t="s">
         <v>454</v>
       </c>
-      <c r="I2" s="60"/>
-      <c r="J2" s="58" t="s">
+      <c r="I2" s="58"/>
+      <c r="J2" s="57" t="s">
         <v>1252</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57" t="s">
+      <c r="K2" s="56"/>
+      <c r="L2" s="56" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15">
+    <row r="3" spans="1:14" ht="16">
       <c r="A3" s="35">
         <v>8</v>
       </c>
@@ -21501,15 +22855,15 @@
       <c r="H3" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="57" t="s">
         <v>1203</v>
       </c>
-      <c r="J3" s="58" t="s">
+      <c r="J3" s="57" t="s">
         <v>1253</v>
       </c>
-      <c r="K3" s="59"/>
-    </row>
-    <row r="4" spans="1:14" ht="15">
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" spans="1:14" ht="16">
       <c r="A4" s="35">
         <v>1</v>
       </c>
@@ -21534,18 +22888,18 @@
       <c r="H4" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="I4" s="58" t="s">
+      <c r="I4" s="57" t="s">
         <v>1196</v>
       </c>
-      <c r="J4" s="58" t="s">
+      <c r="J4" s="57" t="s">
         <v>1255</v>
       </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57" t="s">
+      <c r="K4" s="56"/>
+      <c r="L4" s="56" t="s">
         <v>1254</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15">
+    <row r="5" spans="1:14" ht="16">
       <c r="A5" s="35">
         <v>7</v>
       </c>
@@ -21570,15 +22924,15 @@
       <c r="H5" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="I5" s="58" t="s">
+      <c r="I5" s="57" t="s">
         <v>1202</v>
       </c>
-      <c r="J5" s="58" t="s">
+      <c r="J5" s="57" t="s">
         <v>1256</v>
       </c>
-      <c r="K5" s="59"/>
-    </row>
-    <row r="6" spans="1:14" ht="15">
+      <c r="K5" s="25"/>
+    </row>
+    <row r="6" spans="1:14" ht="16">
       <c r="A6" s="35">
         <v>3</v>
       </c>
@@ -21601,15 +22955,15 @@
         <v>440</v>
       </c>
       <c r="H6" s="35"/>
-      <c r="I6" s="58" t="s">
+      <c r="I6" s="57" t="s">
         <v>1199</v>
       </c>
-      <c r="J6" s="58" t="s">
+      <c r="J6" s="57" t="s">
         <v>1257</v>
       </c>
-      <c r="K6" s="59"/>
-    </row>
-    <row r="7" spans="1:14" ht="15">
+      <c r="K6" s="25"/>
+    </row>
+    <row r="7" spans="1:14" ht="16">
       <c r="A7" s="35">
         <v>2</v>
       </c>
@@ -21632,15 +22986,15 @@
         <v>1258</v>
       </c>
       <c r="H7" s="35"/>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="25" t="s">
         <v>1198</v>
       </c>
-      <c r="J7" s="58" t="s">
+      <c r="J7" s="57" t="s">
         <v>1259</v>
       </c>
-      <c r="K7" s="59"/>
-    </row>
-    <row r="8" spans="1:14" ht="15">
+      <c r="K7" s="25"/>
+    </row>
+    <row r="8" spans="1:14" ht="16">
       <c r="A8" s="35">
         <v>4</v>
       </c>
@@ -21665,15 +23019,15 @@
       <c r="H8" s="35" t="s">
         <v>444</v>
       </c>
-      <c r="I8" s="57" t="s">
+      <c r="I8" s="56" t="s">
         <v>1200</v>
       </c>
-      <c r="J8" s="58" t="s">
+      <c r="J8" s="57" t="s">
         <v>1260</v>
       </c>
-      <c r="K8" s="59"/>
-    </row>
-    <row r="9" spans="1:14" ht="15">
+      <c r="K8" s="25"/>
+    </row>
+    <row r="9" spans="1:14" ht="16">
       <c r="A9" s="35">
         <v>5</v>
       </c>
@@ -21698,15 +23052,15 @@
       <c r="H9" s="35" t="s">
         <v>448</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="56" t="s">
         <v>1201</v>
       </c>
-      <c r="J9" s="58" t="s">
+      <c r="J9" s="57" t="s">
         <v>1261</v>
       </c>
-      <c r="K9" s="59"/>
-    </row>
-    <row r="10" spans="1:14" ht="15">
+      <c r="K9" s="25"/>
+    </row>
+    <row r="10" spans="1:14" ht="16">
       <c r="A10" s="35">
         <v>11</v>
       </c>
@@ -21731,17 +23085,17 @@
       <c r="H10" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="I10" s="57" t="s">
+      <c r="I10" s="56" t="s">
         <v>1207</v>
       </c>
-      <c r="K10" s="59" t="s">
+      <c r="K10" s="25" t="s">
         <v>1287</v>
       </c>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="25" t="s">
         <v>1206</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15">
+    <row r="11" spans="1:14" ht="16">
       <c r="A11" s="35">
         <v>13</v>
       </c>
@@ -21766,14 +23120,14 @@
       <c r="H11" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="I11" s="57" t="s">
+      <c r="I11" s="56" t="s">
         <v>1209</v>
       </c>
-      <c r="K11" s="59" t="s">
+      <c r="K11" s="25" t="s">
         <v>1288</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15">
+    <row r="12" spans="1:14" ht="16">
       <c r="A12" s="35">
         <v>15</v>
       </c>
@@ -21798,10 +23152,10 @@
       <c r="H12" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="I12" s="57" t="s">
+      <c r="I12" s="56" t="s">
         <v>1213</v>
       </c>
-      <c r="K12" s="59" t="s">
+      <c r="K12" s="25" t="s">
         <v>1289</v>
       </c>
       <c r="M12" s="35" t="s">
@@ -21811,7 +23165,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15">
+    <row r="13" spans="1:14" ht="16">
       <c r="A13" s="35">
         <v>9</v>
       </c>
@@ -21836,17 +23190,17 @@
       <c r="H13" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="56" t="s">
         <v>1204</v>
       </c>
-      <c r="K13" s="59" t="s">
+      <c r="K13" s="25" t="s">
         <v>1290</v>
       </c>
       <c r="M13" s="35" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15">
+    <row r="14" spans="1:14" ht="16">
       <c r="A14" s="35">
         <v>10</v>
       </c>
@@ -21871,14 +23225,14 @@
       <c r="H14" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="I14" s="57" t="s">
+      <c r="I14" s="56" t="s">
         <v>1205</v>
       </c>
-      <c r="K14" s="59" t="s">
+      <c r="K14" s="25" t="s">
         <v>1291</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15">
+    <row r="15" spans="1:14" ht="16">
       <c r="A15" s="35">
         <v>16</v>
       </c>
@@ -21903,14 +23257,14 @@
       <c r="H15" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="I15" s="57" t="s">
+      <c r="I15" s="56" t="s">
         <v>1214</v>
       </c>
-      <c r="K15" s="59" t="s">
+      <c r="K15" s="25" t="s">
         <v>1292</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15">
+    <row r="16" spans="1:14" ht="16">
       <c r="A16" s="35">
         <v>17</v>
       </c>
@@ -21935,14 +23289,14 @@
       <c r="H16" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="I16" s="57" t="s">
+      <c r="I16" s="56" t="s">
         <v>1215</v>
       </c>
-      <c r="K16" s="59" t="s">
+      <c r="K16" s="25" t="s">
         <v>1293</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15">
+    <row r="17" spans="1:13" ht="16">
       <c r="A17" s="35">
         <v>12</v>
       </c>
@@ -21965,14 +23319,14 @@
       <c r="H17" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="I17" s="57" t="s">
+      <c r="I17" s="56" t="s">
         <v>1208</v>
       </c>
-      <c r="K17" s="59" t="s">
+      <c r="K17" s="25" t="s">
         <v>1294</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15">
+    <row r="18" spans="1:13" ht="16">
       <c r="A18" s="35">
         <v>14</v>
       </c>
@@ -21995,10 +23349,10 @@
       <c r="H18" s="35" t="s">
         <v>772</v>
       </c>
-      <c r="I18" s="57" t="s">
+      <c r="I18" s="56" t="s">
         <v>1211</v>
       </c>
-      <c r="K18" s="59" t="s">
+      <c r="K18" s="25" t="s">
         <v>1295</v>
       </c>
       <c r="M18" t="s">
@@ -22012,24 +23366,25 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E27160-7128-40E1-9AE3-BF05BBDBFACD}">
   <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="54.109375" customWidth="1"/>
-    <col min="10" max="10" width="12.21875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="54.1640625" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" hidden="1" customWidth="1"/>
     <col min="11" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="41.77734375" customWidth="1"/>
+    <col min="14" max="14" width="41.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15">
+    <row r="1" spans="1:17" ht="16">
       <c r="A1" s="30" t="s">
         <v>783</v>
       </c>
@@ -22054,35 +23409,35 @@
       <c r="H1" s="31" t="s">
         <v>423</v>
       </c>
-      <c r="I1" s="58" t="s">
+      <c r="I1" s="57" t="s">
         <v>1197</v>
       </c>
-      <c r="J1" s="57" t="s">
+      <c r="J1" s="56" t="s">
         <v>1185</v>
       </c>
-      <c r="K1" s="57" t="s">
+      <c r="K1" s="56" t="s">
         <v>1185</v>
       </c>
-      <c r="L1" s="57" t="s">
+      <c r="L1" s="56" t="s">
         <v>1185</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="M1" s="56" t="s">
         <v>1185</v>
       </c>
-      <c r="N1" s="57" t="s">
+      <c r="N1" s="56" t="s">
         <v>1299</v>
       </c>
-      <c r="O1" s="57" t="s">
+      <c r="O1" s="56" t="s">
         <v>1251</v>
       </c>
-      <c r="P1" s="57" t="s">
+      <c r="P1" s="56" t="s">
         <v>1251</v>
       </c>
-      <c r="Q1" s="57" t="s">
+      <c r="Q1" s="56" t="s">
         <v>1297</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15">
+    <row r="2" spans="1:17" ht="16">
       <c r="A2" s="34">
         <v>4</v>
       </c>
@@ -22107,14 +23462,14 @@
       <c r="H2" s="35" t="s">
         <v>509</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>1219</v>
       </c>
       <c r="N2" t="s">
         <v>1279</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15">
+    <row r="3" spans="1:17" ht="16">
       <c r="A3" s="34">
         <v>7</v>
       </c>
@@ -22137,14 +23492,14 @@
         <v>518</v>
       </c>
       <c r="H3" s="35"/>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="57" t="s">
         <v>1231</v>
       </c>
       <c r="N3" t="s">
         <v>1273</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15">
+    <row r="4" spans="1:17" ht="16">
       <c r="A4" s="34">
         <v>8</v>
       </c>
@@ -22167,15 +23522,15 @@
         <v>521</v>
       </c>
       <c r="H4" s="35"/>
-      <c r="I4" s="59" t="s">
+      <c r="I4" s="25" t="s">
         <v>1221</v>
       </c>
-      <c r="K4" s="63"/>
+      <c r="K4" s="60"/>
       <c r="N4" t="s">
         <v>1274</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="14.4" customHeight="1">
+    <row r="5" spans="1:17" ht="14.5" customHeight="1">
       <c r="A5" s="34">
         <v>6</v>
       </c>
@@ -22197,17 +23552,17 @@
       <c r="G5" s="35" t="s">
         <v>425</v>
       </c>
-      <c r="H5" s="64" t="s">
+      <c r="H5" s="61" t="s">
         <v>515</v>
       </c>
-      <c r="I5" s="57" t="s">
+      <c r="I5" s="56" t="s">
         <v>1225</v>
       </c>
       <c r="N5" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15">
+    <row r="6" spans="1:17" ht="16">
       <c r="A6" s="34">
         <v>1</v>
       </c>
@@ -22232,20 +23587,20 @@
       <c r="H6" s="35" t="s">
         <v>500</v>
       </c>
-      <c r="I6" s="57" t="s">
+      <c r="I6" s="56" t="s">
         <v>1217</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
-      <c r="K6" s="59" t="s">
+      <c r="K6" s="25" t="s">
         <v>1216</v>
       </c>
       <c r="N6" t="s">
         <v>1283</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15">
+    <row r="7" spans="1:17" ht="16">
       <c r="A7" s="34">
         <v>9</v>
       </c>
@@ -22270,23 +23625,23 @@
       <c r="H7" s="35" t="s">
         <v>525</v>
       </c>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="56" t="s">
         <v>1223</v>
       </c>
       <c r="J7">
         <v>2</v>
       </c>
-      <c r="K7" s="62" t="s">
+      <c r="K7" s="25" t="s">
         <v>522</v>
       </c>
-      <c r="L7" s="62" t="s">
+      <c r="L7" s="25" t="s">
         <v>1222</v>
       </c>
-      <c r="N7" s="59" t="s">
+      <c r="N7" s="25" t="s">
         <v>1276</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15">
+    <row r="8" spans="1:17" ht="16">
       <c r="A8" s="34">
         <v>5</v>
       </c>
@@ -22309,14 +23664,14 @@
         <v>512</v>
       </c>
       <c r="H8" s="35"/>
-      <c r="I8" s="57" t="s">
+      <c r="I8" s="56" t="s">
         <v>1220</v>
       </c>
       <c r="N8" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15">
+    <row r="9" spans="1:17" ht="16">
       <c r="A9" s="34">
         <v>2</v>
       </c>
@@ -22339,7 +23694,7 @@
       <c r="H9" s="35" t="s">
         <v>504</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="56" t="s">
         <v>1218</v>
       </c>
       <c r="N9" t="s">
@@ -22352,7 +23707,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15">
+    <row r="10" spans="1:17" ht="16">
       <c r="A10" s="34">
         <v>3</v>
       </c>
@@ -22369,7 +23724,7 @@
       <c r="F10" s="35"/>
       <c r="G10" s="35"/>
       <c r="H10" s="35"/>
-      <c r="I10" s="61" t="s">
+      <c r="I10" s="59" t="s">
         <v>1285</v>
       </c>
       <c r="J10">
@@ -22378,12 +23733,12 @@
       <c r="K10" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="L10" s="63"/>
+      <c r="L10" s="60"/>
       <c r="N10" t="s">
         <v>1284</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15">
+    <row r="11" spans="1:17" ht="16">
       <c r="A11" s="34">
         <v>14</v>
       </c>
@@ -22408,14 +23763,14 @@
       <c r="H11" s="35" t="s">
         <v>544</v>
       </c>
-      <c r="I11" s="57" t="s">
+      <c r="I11" s="56" t="s">
         <v>1229</v>
       </c>
-      <c r="N11" s="74" t="s">
+      <c r="N11" t="s">
         <v>1298</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15">
+    <row r="12" spans="1:17" ht="16">
       <c r="A12" s="34">
         <v>13</v>
       </c>
@@ -22440,17 +23795,17 @@
       <c r="H12" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="I12" s="57" t="s">
+      <c r="I12" s="56" t="s">
         <v>1296</v>
       </c>
-      <c r="N12" s="74" t="s">
+      <c r="N12" t="s">
         <v>1300</v>
       </c>
       <c r="Q12" s="35" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15">
+    <row r="13" spans="1:17" ht="16">
       <c r="A13" s="34">
         <v>10</v>
       </c>
@@ -22475,14 +23830,14 @@
       <c r="H13" s="35" t="s">
         <v>529</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="56" t="s">
         <v>1224</v>
       </c>
       <c r="N13" t="s">
         <v>1301</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15">
+    <row r="14" spans="1:17" ht="16">
       <c r="A14" s="34">
         <v>12</v>
       </c>
@@ -22507,14 +23862,14 @@
       <c r="H14" s="35" t="s">
         <v>536</v>
       </c>
-      <c r="I14" s="57" t="s">
+      <c r="I14" s="56" t="s">
         <v>1227</v>
       </c>
       <c r="N14" t="s">
         <v>1302</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15">
+    <row r="15" spans="1:17" ht="16">
       <c r="A15" s="34">
         <v>11</v>
       </c>
@@ -22539,14 +23894,14 @@
       <c r="H15" s="35" t="s">
         <v>532</v>
       </c>
-      <c r="I15" s="57" t="s">
+      <c r="I15" s="56" t="s">
         <v>1304</v>
       </c>
       <c r="N15" t="s">
         <v>1303</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15">
+    <row r="16" spans="1:17" ht="16">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -22579,11 +23934,11 @@
       <c r="M16" s="35" t="s">
         <v>554</v>
       </c>
-      <c r="N16" s="73" t="s">
+      <c r="N16" s="63" t="s">
         <v>1195</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15">
+    <row r="17" spans="1:17" ht="16">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -22606,7 +23961,7 @@
       <c r="H17" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="I17" s="57" t="s">
+      <c r="I17" s="56" t="s">
         <v>1230</v>
       </c>
       <c r="N17" t="s">
@@ -22616,7 +23971,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15">
+    <row r="18" spans="1:17" ht="16">
       <c r="A18" s="41">
         <v>17</v>
       </c>
@@ -22637,7 +23992,7 @@
         <v>551</v>
       </c>
       <c r="H18" s="42"/>
-      <c r="I18" s="57" t="s">
+      <c r="I18" s="56" t="s">
         <v>1232</v>
       </c>
       <c r="J18">
@@ -22649,7 +24004,7 @@
       <c r="L18" s="42" t="s">
         <v>551</v>
       </c>
-      <c r="N18" s="59" t="s">
+      <c r="N18" s="25" t="s">
         <v>1306</v>
       </c>
       <c r="Q18" s="42" t="s">
@@ -22663,13 +24018,14 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A84558C-36C6-4B03-911F-84558FD8E17A}">
   <dimension ref="B1:D4"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="4" width="13.6640625" customWidth="1"/>
   </cols>
@@ -22721,530 +24077,24 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB3C53C-44A1-4C7E-A7C1-EE52E2D3AB9D}">
-  <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
-  <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" s="65">
-        <f>EXP(0.307)</f>
-        <v>1.3593409680719806</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAD788D-949A-49FB-B3CF-88BF7FE61F68}">
-  <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
-  <cols>
-    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="79.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB3C53C-44A1-4C7E-A7C1-EE52E2D3AB9D}">
+  <dimension ref="B2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15">
-      <c r="A1" s="30" t="s">
-        <v>783</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>421</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="H1" s="58" t="s">
-        <v>1197</v>
-      </c>
-      <c r="I1" s="57" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15">
-      <c r="A2" s="34">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>496</v>
-      </c>
-      <c r="C2" s="35">
-        <v>4</v>
-      </c>
-      <c r="D2" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>498</v>
-      </c>
-      <c r="F2" s="35" t="s">
-        <v>499</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>500</v>
-      </c>
-      <c r="H2" s="58" t="s">
-        <v>1217</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" s="59" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15">
-      <c r="A3" s="34">
-        <v>2</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>501</v>
-      </c>
-      <c r="C3" s="35">
-        <v>4</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>502</v>
-      </c>
-      <c r="F3" s="35" t="s">
-        <v>503</v>
-      </c>
-      <c r="G3" s="35" t="s">
-        <v>504</v>
-      </c>
-      <c r="H3" s="58" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15">
-      <c r="A4" s="34">
-        <v>3</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>505</v>
-      </c>
-      <c r="C4" s="35">
-        <v>1</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" s="35" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15">
-      <c r="A5" s="34">
-        <v>4</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>506</v>
-      </c>
-      <c r="C5" s="35">
-        <v>5</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>507</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>508</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>509</v>
-      </c>
-      <c r="H5" s="57" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15">
-      <c r="A6" s="34">
-        <v>5</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>510</v>
-      </c>
-      <c r="C6" s="35">
-        <v>3</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>511</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>512</v>
-      </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="57" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15">
-      <c r="A7" s="34">
-        <v>6</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>513</v>
-      </c>
-      <c r="C7" s="35">
-        <v>5</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>514</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>425</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>515</v>
-      </c>
-      <c r="H7" s="57" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15">
-      <c r="A8" s="34">
-        <v>7</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>516</v>
-      </c>
-      <c r="C8" s="35">
-        <v>3</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>517</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>518</v>
-      </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="57" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15">
-      <c r="A9" s="34">
-        <v>8</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>519</v>
-      </c>
-      <c r="C9" s="35">
-        <v>3</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>520</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>521</v>
-      </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="57" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15">
-      <c r="A10" s="34">
-        <v>9</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>522</v>
-      </c>
-      <c r="C10" s="35">
-        <v>4</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>523</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>524</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>525</v>
-      </c>
-      <c r="H10" s="57" t="s">
-        <v>1223</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>522</v>
-      </c>
-      <c r="K10" s="35" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>526</v>
-      </c>
-      <c r="C11" s="35">
-        <v>4</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>527</v>
-      </c>
-      <c r="F11" s="35" t="s">
-        <v>528</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>529</v>
-      </c>
-      <c r="H11" s="57" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15">
-      <c r="A12" s="34">
-        <v>11</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>530</v>
-      </c>
-      <c r="C12" s="35">
-        <v>4</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>426</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>531</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>532</v>
-      </c>
-      <c r="H12" s="57" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15">
-      <c r="A13" s="34">
-        <v>12</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>533</v>
-      </c>
-      <c r="C13" s="35">
-        <v>4</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>534</v>
-      </c>
-      <c r="F13" s="35" t="s">
-        <v>535</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>536</v>
-      </c>
-      <c r="H13" s="57" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15">
-      <c r="A14" s="34">
-        <v>13</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>537</v>
-      </c>
-      <c r="C14" s="35">
-        <v>4</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>538</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>539</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>540</v>
-      </c>
-      <c r="H14" s="57" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15">
-      <c r="A15" s="34">
-        <v>14</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>541</v>
-      </c>
-      <c r="C15" s="35">
-        <v>4</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>542</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>543</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>544</v>
-      </c>
-      <c r="H15" s="57" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15">
-      <c r="A16" s="34">
-        <v>15</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>552</v>
-      </c>
-      <c r="C16" s="35">
-        <v>3</v>
-      </c>
-      <c r="D16" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>553</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>554</v>
-      </c>
-      <c r="G16" s="35"/>
-      <c r="I16">
-        <v>3</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>552</v>
-      </c>
-      <c r="K16" s="35" t="s">
-        <v>553</v>
-      </c>
-      <c r="L16" s="35" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15">
-      <c r="A17" s="34">
-        <v>16</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>545</v>
-      </c>
-      <c r="C17" s="35">
-        <v>4</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="E17" s="35" t="s">
-        <v>546</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>547</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>548</v>
-      </c>
-      <c r="H17" s="57" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15">
-      <c r="A18" s="41">
-        <v>17</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>549</v>
-      </c>
-      <c r="C18" s="42">
-        <v>3</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>427</v>
-      </c>
-      <c r="E18" s="42" t="s">
-        <v>550</v>
-      </c>
-      <c r="F18" s="42" t="s">
-        <v>551</v>
-      </c>
-      <c r="G18" s="42"/>
-      <c r="H18" s="57" t="s">
-        <v>1232</v>
-      </c>
-      <c r="I18">
-        <v>2</v>
-      </c>
-      <c r="J18" s="42" t="s">
-        <v>549</v>
-      </c>
-      <c r="K18" s="42" t="s">
-        <v>551</v>
+    <row r="2" spans="2:2">
+      <c r="B2" s="62">
+        <f>EXP(0.307)</f>
+        <v>1.3593409680719806</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>